--- a/Design/Excel/ET/Datas/Product/LevelConfig.xlsx
+++ b/Design/Excel/ET/Datas/Product/LevelConfig.xlsx
@@ -1128,7 +1128,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr/>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="6"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -1198,6 +1198,11 @@
           <t>RequireBuffChoice</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>AllowedRenovationIds</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1255,6 +1260,11 @@
           <t>bool</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>(list#sep=,),int</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1312,6 +1322,11 @@
           <t>RequireBuffChoice</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>AllowedRenovationIds</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1369,6 +1384,11 @@
           <t>true</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>1,2</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1424,6 +1444,11 @@
       <c r="K5" t="inlineStr">
         <is>
           <t>true</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>1,2</t>
         </is>
       </c>
     </row>

--- a/Design/Excel/ET/Datas/Product/LevelConfig.xlsx
+++ b/Design/Excel/ET/Datas/Product/LevelConfig.xlsx
@@ -1128,7 +1128,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr/>
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:Q11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="6"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -1203,6 +1203,31 @@
           <t>AllowedRenovationIds</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>ChapterId</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>ChapterStage</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>IsChapterTerminal</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>MenuVariant</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>AllowedDrinkIds</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1265,6 +1290,31 @@
           <t>(list#sep=,),int</t>
         </is>
       </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>(list#sep=,),int</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1327,6 +1377,31 @@
           <t>AllowedRenovationIds</t>
         </is>
       </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>ChapterId</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>ChapterStage</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>IsChapterTerminal</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>MenuVariant</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>AllowedDrinkIds</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1371,7 +1446,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1,2,3</t>
+          <t>1,2,3,4,5</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1387,6 +1462,31 @@
       <c r="L4" t="inlineStr">
         <is>
           <t>1,2</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t/>
         </is>
       </c>
     </row>
@@ -1433,7 +1533,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1,2,3</t>
+          <t>1,2,3,4,5</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1449,6 +1549,553 @@
       <c r="L5" t="inlineStr">
         <is>
           <t>1,2</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>10,20,30</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>1,2</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>1,2,3,4</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>10,20,30</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>1,2</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>1,2,3,4</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>10,20,30</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>1,2</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>10,20,30</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>1,2</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>1,2,3,4</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>10,20,30</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>1,2</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>1,2,3,4</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>10,20,30</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>1,2</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
     </row>

--- a/Design/Excel/ET/Datas/Product/LevelConfig.xlsx
+++ b/Design/Excel/ET/Datas/Product/LevelConfig.xlsx
@@ -1128,7 +1128,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr/>
-  <dimension ref="A1:Q11"/>
+  <dimension ref="A1:Q13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="6"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -2099,6 +2099,180 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>10,20,30</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>1,2</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>5,6</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>10,20,30</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>1,2</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>5,6</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Design/Excel/ET/Datas/Product/LevelConfig.xlsx
+++ b/Design/Excel/ET/Datas/Product/LevelConfig.xlsx
@@ -1,693 +1,731 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UnitProto" sheetId="1" r:id="R7b8d15f1d348473e"/>
-  </x:sheets>
-</x:workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <sheets>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UnitProto" sheetId="1" state="visible" r:id="rId1"/>
+  </sheets>
+  <definedNames/>
+</workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="4">
-    <x:numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <x:numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <x:numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <x:numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </x:numFmts>
-  <x:fonts count="24">
-    <x:font>
-      <x:sz val="11"/>
-      <x:color theme="1"/>
-      <x:name val="宋体"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:sz val="9"/>
-      <x:color theme="1"/>
-      <x:name val="微软雅黑"/>
-    </x:font>
-    <x:font>
-      <x:sz val="11"/>
-      <x:color theme="1"/>
-      <x:name val="微软雅黑"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="9"/>
-      <x:color theme="1"/>
-      <x:name val="微软雅黑"/>
-    </x:font>
-    <x:font>
-      <x:sz val="12"/>
-      <x:color theme="1"/>
-      <x:name val="宋体"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:u val="single"/>
-      <x:sz val="11"/>
-      <x:color rgb="FF0000FF"/>
-      <x:name val="宋体"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:u val="single"/>
-      <x:sz val="11"/>
-      <x:color rgb="FF800080"/>
-      <x:name val="宋体"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:sz val="11"/>
-      <x:color rgb="FFFF0000"/>
-      <x:name val="宋体"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="18"/>
-      <x:color theme="3"/>
-      <x:name val="宋体"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:i/>
-      <x:sz val="11"/>
-      <x:color rgb="FF7F7F7F"/>
-      <x:name val="宋体"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="15"/>
-      <x:color theme="3"/>
-      <x:name val="宋体"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="13"/>
-      <x:color theme="3"/>
-      <x:name val="宋体"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="11"/>
-      <x:color theme="3"/>
-      <x:name val="宋体"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:sz val="11"/>
-      <x:color rgb="FF3F3F76"/>
-      <x:name val="宋体"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="11"/>
-      <x:color rgb="FF3F3F3F"/>
-      <x:name val="宋体"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="11"/>
-      <x:color rgb="FFFA7D00"/>
-      <x:name val="宋体"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="11"/>
-      <x:color rgb="FFFFFFFF"/>
-      <x:name val="宋体"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:sz val="11"/>
-      <x:color rgb="FFFA7D00"/>
-      <x:name val="宋体"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="11"/>
-      <x:color theme="1"/>
-      <x:name val="宋体"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:sz val="11"/>
-      <x:color rgb="FF006100"/>
-      <x:name val="宋体"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:sz val="11"/>
-      <x:color rgb="FF9C0006"/>
-      <x:name val="宋体"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:sz val="11"/>
-      <x:color rgb="FF9C6500"/>
-      <x:name val="宋体"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:sz val="11"/>
-      <x:color theme="0"/>
-      <x:name val="宋体"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:sz val="11"/>
-      <x:color theme="1"/>
-      <x:name val="宋体"/>
-      <x:scheme val="minor"/>
-    </x:font>
-  </x:fonts>
-  <x:fills count="34">
-    <x:fill>
-      <x:patternFill patternType="none"/>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="gray125"/>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF92D050"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFFFFCC"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFFCC99"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFF2F2F2"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFA5A5A5"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFC6EFCE"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFFC7CE"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFFEB9C"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="4"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="4" tint="0.79998"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="4" tint="0.59999"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="4" tint="0.39998"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="5"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="5" tint="0.79998"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="5" tint="0.59999"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="5" tint="0.39998"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="6"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="6" tint="0.79998"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="6" tint="0.59999"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="6" tint="0.39998"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="7"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="7" tint="0.79998"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="7" tint="0.59999"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="7" tint="0.39998"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="8"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="8" tint="0.79998"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="8" tint="0.59999"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="8" tint="0.39998"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="9"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="9" tint="0.79998"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="9" tint="0.59999"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="9" tint="0.39998"/>
-      </x:patternFill>
-    </x:fill>
-  </x:fills>
-  <x:borders count="9">
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-      <x:diagonal/>
-    </x:border>
-    <x:border>
-      <x:left style="thin">
-        <x:color rgb="FFB2B2B2"/>
-      </x:left>
-      <x:right style="thin">
-        <x:color rgb="FFB2B2B2"/>
-      </x:right>
-      <x:top style="thin">
-        <x:color rgb="FFB2B2B2"/>
-      </x:top>
-      <x:bottom style="thin">
-        <x:color rgb="FFB2B2B2"/>
-      </x:bottom>
-      <x:diagonal/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom style="medium">
-        <x:color theme="4"/>
-      </x:bottom>
-      <x:diagonal/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom style="medium">
-        <x:color theme="4" tint="0.49998"/>
-      </x:bottom>
-      <x:diagonal/>
-    </x:border>
-    <x:border>
-      <x:left style="thin">
-        <x:color rgb="FF7F7F7F"/>
-      </x:left>
-      <x:right style="thin">
-        <x:color rgb="FF7F7F7F"/>
-      </x:right>
-      <x:top style="thin">
-        <x:color rgb="FF7F7F7F"/>
-      </x:top>
-      <x:bottom style="thin">
-        <x:color rgb="FF7F7F7F"/>
-      </x:bottom>
-      <x:diagonal/>
-    </x:border>
-    <x:border>
-      <x:left style="thin">
-        <x:color rgb="FF3F3F3F"/>
-      </x:left>
-      <x:right style="thin">
-        <x:color rgb="FF3F3F3F"/>
-      </x:right>
-      <x:top style="thin">
-        <x:color rgb="FF3F3F3F"/>
-      </x:top>
-      <x:bottom style="thin">
-        <x:color rgb="FF3F3F3F"/>
-      </x:bottom>
-      <x:diagonal/>
-    </x:border>
-    <x:border>
-      <x:left style="double">
-        <x:color rgb="FF3F3F3F"/>
-      </x:left>
-      <x:right style="double">
-        <x:color rgb="FF3F3F3F"/>
-      </x:right>
-      <x:top style="double">
-        <x:color rgb="FF3F3F3F"/>
-      </x:top>
-      <x:bottom style="double">
-        <x:color rgb="FF3F3F3F"/>
-      </x:bottom>
-      <x:diagonal/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom style="double">
-        <x:color rgb="FFFF8001"/>
-      </x:bottom>
-      <x:diagonal/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top style="thin">
-        <x:color theme="4"/>
-      </x:top>
-      <x:bottom style="double">
-        <x:color theme="4"/>
-      </x:bottom>
-      <x:diagonal/>
-    </x:border>
-  </x:borders>
-  <x:cellStyleXfs count="50">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <x:xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="15" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="16" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-  </x:cellStyleXfs>
-  <x:cellXfs count="7">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <x:extLst>
-        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
-        </x:ext>
-      </x:extLst>
-    </x:xf>
-  </x:cellXfs>
-  <x:cellStyles count="50">
-    <x:cellStyle name="常规" xfId="0"/>
-    <x:cellStyle name="千位分隔" xfId="1"/>
-    <x:cellStyle name="货币" xfId="2"/>
-    <x:cellStyle name="百分比" xfId="3"/>
-    <x:cellStyle name="千位分隔[0]" xfId="4"/>
-    <x:cellStyle name="货币[0]" xfId="5"/>
-    <x:cellStyle name="超链接" xfId="6"/>
-    <x:cellStyle name="已访问的超链接" xfId="7"/>
-    <x:cellStyle name="注释" xfId="8"/>
-    <x:cellStyle name="警告文本" xfId="9"/>
-    <x:cellStyle name="标题" xfId="10"/>
-    <x:cellStyle name="解释性文本" xfId="11"/>
-    <x:cellStyle name="标题 1" xfId="12"/>
-    <x:cellStyle name="标题 2" xfId="13"/>
-    <x:cellStyle name="标题 3" xfId="14"/>
-    <x:cellStyle name="标题 4" xfId="15"/>
-    <x:cellStyle name="输入" xfId="16"/>
-    <x:cellStyle name="输出" xfId="17"/>
-    <x:cellStyle name="计算" xfId="18"/>
-    <x:cellStyle name="检查单元格" xfId="19"/>
-    <x:cellStyle name="链接单元格" xfId="20"/>
-    <x:cellStyle name="汇总" xfId="21"/>
-    <x:cellStyle name="好" xfId="22"/>
-    <x:cellStyle name="差" xfId="23"/>
-    <x:cellStyle name="适中" xfId="24"/>
-    <x:cellStyle name="强调文字颜色 1" xfId="25"/>
-    <x:cellStyle name="20% - 强调文字颜色 1" xfId="26"/>
-    <x:cellStyle name="40% - 强调文字颜色 1" xfId="27"/>
-    <x:cellStyle name="60% - 强调文字颜色 1" xfId="28"/>
-    <x:cellStyle name="强调文字颜色 2" xfId="29"/>
-    <x:cellStyle name="20% - 强调文字颜色 2" xfId="30"/>
-    <x:cellStyle name="40% - 强调文字颜色 2" xfId="31"/>
-    <x:cellStyle name="60% - 强调文字颜色 2" xfId="32"/>
-    <x:cellStyle name="强调文字颜色 3" xfId="33"/>
-    <x:cellStyle name="20% - 强调文字颜色 3" xfId="34"/>
-    <x:cellStyle name="40% - 强调文字颜色 3" xfId="35"/>
-    <x:cellStyle name="60% - 强调文字颜色 3" xfId="36"/>
-    <x:cellStyle name="强调文字颜色 4" xfId="37"/>
-    <x:cellStyle name="20% - 强调文字颜色 4" xfId="38"/>
-    <x:cellStyle name="40% - 强调文字颜色 4" xfId="39"/>
-    <x:cellStyle name="60% - 强调文字颜色 4" xfId="40"/>
-    <x:cellStyle name="强调文字颜色 5" xfId="41"/>
-    <x:cellStyle name="20% - 强调文字颜色 5" xfId="42"/>
-    <x:cellStyle name="40% - 强调文字颜色 5" xfId="43"/>
-    <x:cellStyle name="60% - 强调文字颜色 5" xfId="44"/>
-    <x:cellStyle name="强调文字颜色 6" xfId="45"/>
-    <x:cellStyle name="20% - 强调文字颜色 6" xfId="46"/>
-    <x:cellStyle name="40% - 强调文字颜色 6" xfId="47"/>
-    <x:cellStyle name="60% - 强调文字颜色 6" xfId="48"/>
-    <x:cellStyle name="常规 2" xfId="49"/>
-  </x:cellStyles>
-</x:styleSheet>
-</file>
-
-<file path=xl/featurePropertyBag/featurePropertyBag.xml><?xml version="1.0" encoding="utf-8"?>
-<xfpb:FeaturePropertyBags xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag">
-  <xfpb:bag type="Checkbox"/>
-  <xfpb:bag type="XFControls">
-    <xfpb:bagId k="CellControl">0</xfpb:bagId>
-  </xfpb:bag>
-  <xfpb:bag type="XFComplement">
-    <xfpb:bagId k="XFControls">1</xfpb:bagId>
-  </xfpb:bag>
-  <xfpb:bag type="XFComplements" extRef="XFComplementsMapperExtRef">
-    <xfpb:a k="MappedFeaturePropertyBags">
-      <xfpb:bagId>2</xfpb:bagId>
-    </xfpb:a>
-  </xfpb:bag>
-</xfpb:FeaturePropertyBags>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="24">
+    <font>
+      <name val="宋体"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <color theme="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <color theme="1"/>
+      <sz val="12"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <color theme="0"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+  </fonts>
+  <fills count="34">
+    <fill>
+      <patternFill/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39998"/>
+      </patternFill>
+    </fill>
+  </fills>
+  <borders count="9">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.49998"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+  </borders>
+  <cellStyleXfs count="50">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="7">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  </cellXfs>
+  <cellStyles count="50">
+    <cellStyle name="常规" xfId="0"/>
+    <cellStyle name="千位分隔" xfId="1"/>
+    <cellStyle name="货币" xfId="2"/>
+    <cellStyle name="百分比" xfId="3"/>
+    <cellStyle name="千位分隔[0]" xfId="4"/>
+    <cellStyle name="货币[0]" xfId="5"/>
+    <cellStyle name="超链接" xfId="6"/>
+    <cellStyle name="已访问的超链接" xfId="7"/>
+    <cellStyle name="注释" xfId="8"/>
+    <cellStyle name="警告文本" xfId="9"/>
+    <cellStyle name="标题" xfId="10"/>
+    <cellStyle name="解释性文本" xfId="11"/>
+    <cellStyle name="标题 1" xfId="12"/>
+    <cellStyle name="标题 2" xfId="13"/>
+    <cellStyle name="标题 3" xfId="14"/>
+    <cellStyle name="标题 4" xfId="15"/>
+    <cellStyle name="输入" xfId="16"/>
+    <cellStyle name="输出" xfId="17"/>
+    <cellStyle name="计算" xfId="18"/>
+    <cellStyle name="检查单元格" xfId="19"/>
+    <cellStyle name="链接单元格" xfId="20"/>
+    <cellStyle name="汇总" xfId="21"/>
+    <cellStyle name="好" xfId="22"/>
+    <cellStyle name="差" xfId="23"/>
+    <cellStyle name="适中" xfId="24"/>
+    <cellStyle name="强调文字颜色 1" xfId="25"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28"/>
+    <cellStyle name="强调文字颜色 2" xfId="29"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32"/>
+    <cellStyle name="强调文字颜色 3" xfId="33"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36"/>
+    <cellStyle name="强调文字颜色 4" xfId="37"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40"/>
+    <cellStyle name="强调文字颜色 5" xfId="41"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44"/>
+    <cellStyle name="强调文字颜色 6" xfId="45"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48"/>
+    <cellStyle name="常规 2" xfId="49"/>
+  </cellStyles>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
+</styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -964,189 +1002,200 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:T85"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="12.75" style="2" customWidth="1"/>
-    <col min="3" max="4" width="12.625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="15.125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="9.625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="28.75" style="2" customWidth="1"/>
-    <col min="8" max="9" width="11.75" style="2" customWidth="1"/>
-    <col min="10" max="10" width="6.75" style="2" customWidth="1"/>
-    <col min="11" max="16384" width="9" style="2" customWidth="0"/>
+    <col width="21.125" customWidth="1" style="2" min="1" max="1"/>
+    <col width="12.75" customWidth="1" style="2" min="2" max="2"/>
+    <col width="12.625" customWidth="1" style="2" min="3" max="4"/>
+    <col width="15.125" customWidth="1" style="2" min="5" max="5"/>
+    <col width="9.625" customWidth="1" style="2" min="6" max="6"/>
+    <col width="28.75" customWidth="1" style="2" min="7" max="7"/>
+    <col width="11.75" customWidth="1" style="2" min="8" max="9"/>
+    <col width="6.75" customWidth="1" style="2" min="10" max="10"/>
+    <col width="9" customWidth="1" style="2" min="11" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">##var</t>
+          <t>##var</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Id</t>
+          <t>Id</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">NextLevelConfigId</t>
+          <t>NextLevelConfigId</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">OperatingTicks</t>
+          <t>OperatingTicks</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t xml:space="preserve">StarThresholds</t>
+          <t>StarThresholds</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t xml:space="preserve">SpawnX</t>
+          <t>SpawnX</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t xml:space="preserve">SpawnY</t>
+          <t>SpawnY</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t xml:space="preserve">AllowedDishIds</t>
+          <t>AllowedDishIds</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t xml:space="preserve">AllowedBuffIds</t>
+          <t>AllowedBuffIds</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">CandidateCount</t>
+          <t>CandidateCount</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t xml:space="preserve">RequireBuffChoice</t>
+          <t>RequireBuffChoice</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t xml:space="preserve">AllowedRenovationIds</t>
+          <t>AllowedRenovationIds</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ChapterId</t>
+          <t>ChapterId</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ChapterStage</t>
+          <t>ChapterStage</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t xml:space="preserve">IsChapterTerminal</t>
+          <t>IsChapterTerminal</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t xml:space="preserve">MenuVariant</t>
+          <t>MenuVariant</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t xml:space="preserve">AllowedDrinkIds</t>
-        </is>
-      </c>
-      <c r="R1" t="str">
-        <v>UseInitialUnlockSet</v>
-      </c>
-      <c r="S1" t="str">
-        <v>InitialUnlockedDishIds</v>
-      </c>
-      <c r="T1" t="str">
-        <v>InitialUnlockedStationIds</v>
+          <t>AllowedDrinkIds</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>UseInitialUnlockSet</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>InitialUnlockedDishIds</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>InitialUnlockedStationIds</t>
+        </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">##type</t>
+          <t>##type</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">int</t>
+          <t>int</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">int</t>
+          <t>int</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">int</t>
+          <t>int</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(list#sep=,),int</t>
+          <t>(list#sep=,),int</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">int</t>
+          <t>int</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">int</t>
+          <t>int</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(list#sep=,),int</t>
+          <t>(list#sep=,),int</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(list#sep=,),int</t>
+          <t>(list#sep=,),int</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t xml:space="preserve">int</t>
+          <t>int</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t xml:space="preserve">bool</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(list#sep=,),int</t>
+          <t>(list#sep=,),int</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t xml:space="preserve">int</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t xml:space="preserve">int</t>
+          <t>int</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t xml:space="preserve">bool</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -1156,189 +1205,196 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(list#sep=,),int</t>
-        </is>
-      </c>
-      <c r="R2" t="str">
-        <v>bool</v>
-      </c>
-      <c r="S2" t="str">
-        <v>(list#sep=,),int</v>
-      </c>
-      <c r="T2" t="str">
-        <v>(list#sep=,),int</v>
+          <t>(list#sep=,),int</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>(list#sep=,),int</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>(list#sep=,),int</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">##</t>
+          <t>##</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Id</t>
+          <t>Id</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">NextLevelConfigId</t>
+          <t>NextLevelConfigId</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">OperatingTicks</t>
+          <t>OperatingTicks</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">StarThresholds</t>
+          <t>StarThresholds</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">SpawnX</t>
+          <t>SpawnX</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">SpawnY</t>
+          <t>SpawnY</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t xml:space="preserve">AllowedDishIds</t>
+          <t>AllowedDishIds</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t xml:space="preserve">AllowedBuffIds</t>
+          <t>AllowedBuffIds</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CandidateCount</t>
+          <t>CandidateCount</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t xml:space="preserve">RequireBuffChoice</t>
+          <t>RequireBuffChoice</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t xml:space="preserve">AllowedRenovationIds</t>
+          <t>AllowedRenovationIds</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ChapterId</t>
+          <t>ChapterId</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ChapterStage</t>
+          <t>ChapterStage</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t xml:space="preserve">IsChapterTerminal</t>
+          <t>IsChapterTerminal</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t xml:space="preserve">MenuVariant</t>
+          <t>MenuVariant</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t xml:space="preserve">AllowedDrinkIds</t>
-        </is>
-      </c>
-      <c r="R3" t="str">
-        <v>显式初始解锁</v>
-      </c>
-      <c r="S3" t="str">
-        <v>初始菜品定义</v>
-      </c>
-      <c r="T3" t="str">
-        <v>初始设备定义</v>
+          <t>AllowedDrinkIds</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>显式初始解锁</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>初始菜品定义</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>初始设备定义</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">400</t>
+          <t>400</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">10,20,30</t>
+          <t>10,20,30</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1,2</t>
+          <t>1,2</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1,2,3,4,5</t>
+          <t>1,2,3,4,5</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t xml:space="preserve">true</t>
+          <t>true</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1,2,3,4</t>
+          <t>1,2,3,4</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t>false</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -1346,91 +1402,79 @@
           <t>Basic</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="R4" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="S4" t="str"/>
-      <c r="T4" t="str"/>
+      <c r="R4" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">400</t>
+          <t>400</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">10,20,30</t>
+          <t>10,20,30</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t xml:space="preserve">1,2</t>
+          <t>1,2</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t xml:space="preserve">1,2,3,4,5</t>
+          <t>1,2,3,4,5</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t xml:space="preserve">true</t>
+          <t>true</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t xml:space="preserve">1,2,3,4</t>
+          <t>1,2,3,4</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t>false</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1438,91 +1482,79 @@
           <t>Basic</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="R5" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="S5" t="str"/>
-      <c r="T5" t="str"/>
+      <c r="R5" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">101</t>
+          <t>101</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">102</t>
+          <t>102</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">400</t>
+          <t>400</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">10,20,30</t>
+          <t>10,20,30</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">1,2</t>
+          <t>1,2</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t xml:space="preserve">1,2,3,4,5</t>
+          <t>1,2,3,4,5</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t xml:space="preserve">true</t>
+          <t>true</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t xml:space="preserve">1,2,3,4</t>
+          <t>1,2,3,4</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t>false</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1530,91 +1562,79 @@
           <t>Basic</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="R6" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="S6" t="str"/>
-      <c r="T6" t="str"/>
+      <c r="R6" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">102</t>
+          <t>102</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">103</t>
+          <t>103</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">400</t>
+          <t>400</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">10,20,30</t>
+          <t>10,20,30</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">1,2</t>
+          <t>1,2</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t xml:space="preserve">1,2,3,4,5</t>
+          <t>1,2,3,4,5</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t xml:space="preserve">true</t>
+          <t>true</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t xml:space="preserve">1,2,3,4</t>
+          <t>1,2,3,4</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t>false</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1622,91 +1642,74 @@
           <t>Basic</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="R7" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="S7" t="str"/>
-      <c r="T7" t="str"/>
+      <c r="R7" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">103</t>
+          <t>103</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">400</t>
+          <t>400</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">10,20,30</t>
+          <t>10,20,30</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1,2</t>
+          <t>1,2</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1,2,3,4,5</t>
+          <t>1,2,3,4,5</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t xml:space="preserve">true</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>true</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t xml:space="preserve">true</t>
+          <t>true</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1714,91 +1717,79 @@
           <t>Basic</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="R8" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="S8" t="str"/>
-      <c r="T8" t="str"/>
+      <c r="R8" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">201</t>
+          <t>201</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">202</t>
+          <t>202</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">400</t>
+          <t>400</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">10,20,30</t>
+          <t>10,20,30</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">1,2</t>
+          <t>1,2</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t xml:space="preserve">1,2,3,4,5</t>
+          <t>1,2,3,4,5</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t xml:space="preserve">true</t>
+          <t>true</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t xml:space="preserve">1,2,3,4</t>
+          <t>1,2,3,4</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t>false</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1808,89 +1799,82 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="R9" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="S9" t="str"/>
-      <c r="T9" t="str"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R9" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">202</t>
+          <t>202</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">203</t>
+          <t>203</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">400</t>
+          <t>400</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">10,20,30</t>
+          <t>10,20,30</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">1,2</t>
+          <t>1,2</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t xml:space="preserve">1,2,3,4,5</t>
+          <t>1,2,3,4,5</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t xml:space="preserve">true</t>
+          <t>true</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t xml:space="preserve">1,2,3,4</t>
+          <t>1,2,3,4</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t>false</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1900,89 +1884,77 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="R10" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="S10" t="str"/>
-      <c r="T10" t="str"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R10" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">203</t>
+          <t>203</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">400</t>
+          <t>400</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">10,20,30</t>
+          <t>10,20,30</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1,2</t>
+          <t>1,2</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1,2,3,4,5</t>
+          <t>1,2,3,4,5</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t xml:space="preserve">true</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>true</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t xml:space="preserve">true</t>
+          <t>true</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1992,89 +1964,82 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="R11" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="S11" t="str"/>
-      <c r="T11" t="str"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R11" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">400</t>
+          <t>400</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">10,20,30</t>
+          <t>10,20,30</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">1,2</t>
+          <t>1,2</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t xml:space="preserve">1,2,3,4,5</t>
+          <t>1,2,3,4,5</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t xml:space="preserve">true</t>
+          <t>true</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t xml:space="preserve">3,4,5,6</t>
+          <t>3,4,5,6</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t>false</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -2084,89 +2049,82 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="R12" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="S12" t="str"/>
-      <c r="T12" t="str"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R12" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">400</t>
+          <t>400</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">10,20,30</t>
+          <t>10,20,30</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve">1,2</t>
+          <t>1,2</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t xml:space="preserve">1,2,3,4,5</t>
+          <t>1,2,3,4,5</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t xml:space="preserve">true</t>
+          <t>true</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t xml:space="preserve">3,4,5,6</t>
+          <t>3,4,5,6</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t>false</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2176,89 +2134,82 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="R13" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="S13" t="str"/>
-      <c r="T13" t="str"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R13" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">301</t>
+          <t>301</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">302</t>
+          <t>302</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">400</t>
+          <t>400</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">10,20,30</t>
+          <t>10,20,30</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">1,2</t>
+          <t>1,2</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t xml:space="preserve">1,2,3,4,5</t>
+          <t>1,2,3,4,5</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t xml:space="preserve">true</t>
+          <t>true</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t xml:space="preserve">1,2,3,4</t>
+          <t>1,2,3,4</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t>false</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2266,91 +2217,79 @@
           <t>Basic</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="R14" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="S14" t="str"/>
-      <c r="T14" t="str"/>
+      <c r="R14" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">302</t>
+          <t>302</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">303</t>
+          <t>303</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">400</t>
+          <t>400</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">10,20,30</t>
+          <t>10,20,30</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">1,2</t>
+          <t>1,2</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t xml:space="preserve">1,2,3,4,5</t>
+          <t>1,2,3,4,5</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t xml:space="preserve">true</t>
+          <t>true</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t xml:space="preserve">1,2,3,4</t>
+          <t>1,2,3,4</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t>false</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2358,91 +2297,74 @@
           <t>Basic</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="R15" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="S15" t="str"/>
-      <c r="T15" t="str"/>
+      <c r="R15" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">303</t>
+          <t>303</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">400</t>
+          <t>400</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">10,20,30</t>
+          <t>10,20,30</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">1,2</t>
+          <t>1,2</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t xml:space="preserve">1,2,3,4,5</t>
+          <t>1,2,3,4,5</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t xml:space="preserve">true</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>true</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t xml:space="preserve">true</t>
+          <t>true</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2450,91 +2372,79 @@
           <t>Basic</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="R16" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="S16" t="str"/>
-      <c r="T16" t="str"/>
+      <c r="R16" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">401</t>
+          <t>401</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">402</t>
+          <t>402</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">400</t>
+          <t>400</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">10,20,30</t>
+          <t>10,20,30</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">1,2</t>
+          <t>1,2</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t xml:space="preserve">1,2,3,4,5</t>
+          <t>1,2,3,4,5</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t xml:space="preserve">true</t>
+          <t>true</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t xml:space="preserve">3,4,5,6</t>
+          <t>3,4,5,6</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t>false</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2544,89 +2454,82 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="R17" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="S17" t="str"/>
-      <c r="T17" t="str"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R17" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">402</t>
+          <t>402</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">403</t>
+          <t>403</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">400</t>
+          <t>400</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">10,20,30</t>
+          <t>10,20,30</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">1,2</t>
+          <t>1,2</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t xml:space="preserve">1,2,3,4,5</t>
+          <t>1,2,3,4,5</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t xml:space="preserve">true</t>
+          <t>true</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t xml:space="preserve">3,4,5,6</t>
+          <t>3,4,5,6</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t>false</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2636,89 +2539,77 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="R18" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="S18" t="str"/>
-      <c r="T18" t="str"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R18" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">403</t>
+          <t>403</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">400</t>
+          <t>400</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">10,20,30</t>
+          <t>10,20,30</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">1,2</t>
+          <t>1,2</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t xml:space="preserve">1,2,3,4,5</t>
+          <t>1,2,3,4,5</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t xml:space="preserve">true</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>true</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t xml:space="preserve">true</t>
+          <t>true</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2728,17 +2619,14 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="R19" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="S19" t="str"/>
-      <c r="T19" t="str"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R19" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" t="str"/>
       <c r="B20" t="n">
         <v>501</v>
       </c>
@@ -2748,8 +2636,10 @@
       <c r="D20" t="n">
         <v>1200</v>
       </c>
-      <c r="E20" t="str">
-        <v>10,20,30</v>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>10,20,30</t>
+        </is>
       </c>
       <c r="F20" t="n">
         <v>1</v>
@@ -2757,8 +2647,10 @@
       <c r="G20" t="n">
         <v>10</v>
       </c>
-      <c r="H20" t="str">
-        <v>4,5</v>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>4,5</t>
+        </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -2768,7 +2660,7 @@
       <c r="J20" t="n">
         <v>2</v>
       </c>
-      <c r="K20" s="6" t="b">
+      <c r="K20" t="b">
         <v>1</v>
       </c>
       <c r="L20" t="inlineStr">
@@ -2782,7 +2674,7 @@
       <c r="N20" t="n">
         <v>1</v>
       </c>
-      <c r="O20" s="6" t="b">
+      <c r="O20" t="b">
         <v>0</v>
       </c>
       <c r="P20" t="inlineStr">
@@ -2790,15 +2682,11 @@
           <t>Salad</t>
         </is>
       </c>
-      <c r="Q20" t="str"/>
-      <c r="R20" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="S20" t="str"/>
-      <c r="T20" t="str"/>
+      <c r="R20" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" t="str"/>
       <c r="B21" t="n">
         <v>502</v>
       </c>
@@ -2808,8 +2696,10 @@
       <c r="D21" t="n">
         <v>1200</v>
       </c>
-      <c r="E21" t="str">
-        <v>10,20,30</v>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>10,20,30</t>
+        </is>
       </c>
       <c r="F21" t="n">
         <v>1</v>
@@ -2817,8 +2707,10 @@
       <c r="G21" t="n">
         <v>10</v>
       </c>
-      <c r="H21" t="str">
-        <v>4,5</v>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>4,5</t>
+        </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2828,7 +2720,7 @@
       <c r="J21" t="n">
         <v>2</v>
       </c>
-      <c r="K21" s="6" t="b">
+      <c r="K21" t="b">
         <v>1</v>
       </c>
       <c r="L21" t="inlineStr">
@@ -2842,7 +2734,7 @@
       <c r="N21" t="n">
         <v>2</v>
       </c>
-      <c r="O21" s="6" t="b">
+      <c r="O21" t="b">
         <v>0</v>
       </c>
       <c r="P21" t="inlineStr">
@@ -2850,15 +2742,11 @@
           <t>Salad</t>
         </is>
       </c>
-      <c r="Q21" t="str"/>
-      <c r="R21" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="S21" t="str"/>
-      <c r="T21" t="str"/>
+      <c r="R21" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" t="str"/>
       <c r="B22" t="n">
         <v>503</v>
       </c>
@@ -2868,8 +2756,10 @@
       <c r="D22" t="n">
         <v>1200</v>
       </c>
-      <c r="E22" t="str">
-        <v>10,20,30</v>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>10,20,30</t>
+        </is>
       </c>
       <c r="F22" t="n">
         <v>1</v>
@@ -2877,8 +2767,10 @@
       <c r="G22" t="n">
         <v>10</v>
       </c>
-      <c r="H22" t="str">
-        <v>4,5</v>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>4,5</t>
+        </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -2888,17 +2780,16 @@
       <c r="J22" t="n">
         <v>2</v>
       </c>
-      <c r="K22" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="L22" t="str"/>
+      <c r="K22" t="b">
+        <v>1</v>
+      </c>
       <c r="M22" t="n">
         <v>1</v>
       </c>
       <c r="N22" t="n">
         <v>3</v>
       </c>
-      <c r="O22" s="6" t="b">
+      <c r="O22" t="b">
         <v>1</v>
       </c>
       <c r="P22" t="inlineStr">
@@ -2906,15 +2797,11 @@
           <t>Salad</t>
         </is>
       </c>
-      <c r="Q22" t="str"/>
-      <c r="R22" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="S22" t="str"/>
-      <c r="T22" t="str"/>
+      <c r="R22" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" t="str"/>
       <c r="B23" t="n">
         <v>601</v>
       </c>
@@ -2924,8 +2811,10 @@
       <c r="D23" t="n">
         <v>1200</v>
       </c>
-      <c r="E23" t="str">
-        <v>10,20,30</v>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>10,20,30</t>
+        </is>
       </c>
       <c r="F23" t="n">
         <v>1</v>
@@ -2933,8 +2822,10 @@
       <c r="G23" t="n">
         <v>10</v>
       </c>
-      <c r="H23" t="str">
-        <v>4,5</v>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>4,5</t>
+        </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -2944,7 +2835,7 @@
       <c r="J23" t="n">
         <v>2</v>
       </c>
-      <c r="K23" s="6" t="b">
+      <c r="K23" t="b">
         <v>1</v>
       </c>
       <c r="L23" t="inlineStr">
@@ -2958,7 +2849,7 @@
       <c r="N23" t="n">
         <v>1</v>
       </c>
-      <c r="O23" s="6" t="b">
+      <c r="O23" t="b">
         <v>0</v>
       </c>
       <c r="P23" t="inlineStr">
@@ -2966,15 +2857,11 @@
           <t>Salad</t>
         </is>
       </c>
-      <c r="Q23" t="str"/>
-      <c r="R23" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="S23" t="str"/>
-      <c r="T23" t="str"/>
+      <c r="R23" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" t="str"/>
       <c r="B24" t="n">
         <v>602</v>
       </c>
@@ -2984,8 +2871,10 @@
       <c r="D24" t="n">
         <v>1200</v>
       </c>
-      <c r="E24" t="str">
-        <v>10,20,30</v>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>10,20,30</t>
+        </is>
       </c>
       <c r="F24" t="n">
         <v>1</v>
@@ -2993,8 +2882,10 @@
       <c r="G24" t="n">
         <v>10</v>
       </c>
-      <c r="H24" t="str">
-        <v>4,5</v>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>4,5</t>
+        </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -3004,7 +2895,7 @@
       <c r="J24" t="n">
         <v>2</v>
       </c>
-      <c r="K24" s="6" t="b">
+      <c r="K24" t="b">
         <v>1</v>
       </c>
       <c r="L24" t="inlineStr">
@@ -3018,7 +2909,7 @@
       <c r="N24" t="n">
         <v>2</v>
       </c>
-      <c r="O24" s="6" t="b">
+      <c r="O24" t="b">
         <v>0</v>
       </c>
       <c r="P24" t="inlineStr">
@@ -3026,15 +2917,11 @@
           <t>Salad</t>
         </is>
       </c>
-      <c r="Q24" t="str"/>
-      <c r="R24" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="S24" t="str"/>
-      <c r="T24" t="str"/>
+      <c r="R24" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" t="str"/>
       <c r="B25" t="n">
         <v>603</v>
       </c>
@@ -3044,8 +2931,10 @@
       <c r="D25" t="n">
         <v>1200</v>
       </c>
-      <c r="E25" t="str">
-        <v>10,20,30</v>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>10,20,30</t>
+        </is>
       </c>
       <c r="F25" t="n">
         <v>1</v>
@@ -3053,8 +2942,10 @@
       <c r="G25" t="n">
         <v>10</v>
       </c>
-      <c r="H25" t="str">
-        <v>4,5</v>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>4,5</t>
+        </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -3064,17 +2955,16 @@
       <c r="J25" t="n">
         <v>2</v>
       </c>
-      <c r="K25" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="L25" t="str"/>
+      <c r="K25" t="b">
+        <v>1</v>
+      </c>
       <c r="M25" t="n">
         <v>2</v>
       </c>
       <c r="N25" t="n">
         <v>3</v>
       </c>
-      <c r="O25" s="6" t="b">
+      <c r="O25" t="b">
         <v>1</v>
       </c>
       <c r="P25" t="inlineStr">
@@ -3082,15 +2972,11 @@
           <t>Salad</t>
         </is>
       </c>
-      <c r="Q25" t="str"/>
-      <c r="R25" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="S25" t="str"/>
-      <c r="T25" t="str"/>
+      <c r="R25" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" t="str"/>
       <c r="B26" t="n">
         <v>701</v>
       </c>
@@ -3100,8 +2986,10 @@
       <c r="D26" t="n">
         <v>400</v>
       </c>
-      <c r="E26" t="str">
-        <v>10,20,30</v>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>10,20,30</t>
+        </is>
       </c>
       <c r="F26" t="n">
         <v>1</v>
@@ -3109,8 +2997,10 @@
       <c r="G26" t="n">
         <v>10</v>
       </c>
-      <c r="H26" t="str">
-        <v>1,2,4,5</v>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>1,2,4,5</t>
+        </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -3120,7 +3010,7 @@
       <c r="J26" t="n">
         <v>2</v>
       </c>
-      <c r="K26" s="6" t="b">
+      <c r="K26" t="b">
         <v>1</v>
       </c>
       <c r="L26" t="inlineStr">
@@ -3134,7 +3024,7 @@
       <c r="N26" t="n">
         <v>1</v>
       </c>
-      <c r="O26" s="6" t="b">
+      <c r="O26" t="b">
         <v>0</v>
       </c>
       <c r="P26" t="inlineStr">
@@ -3142,21 +3032,26 @@
           <t>Growth</t>
         </is>
       </c>
-      <c r="Q26" t="str">
-        <v>3</v>
-      </c>
-      <c r="R26" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="S26" t="str">
-        <v>1,2,4,5</v>
-      </c>
-      <c r="T26" t="str">
-        <v>1,2,3,4,5,6,7,8,9,11</v>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R26" t="b">
+        <v>1</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>1,2,4,5</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,11</t>
+        </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="str"/>
       <c r="B27" t="n">
         <v>702</v>
       </c>
@@ -3166,8 +3061,10 @@
       <c r="D27" t="n">
         <v>400</v>
       </c>
-      <c r="E27" t="str">
-        <v>10,20,30</v>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>10,20,30</t>
+        </is>
       </c>
       <c r="F27" t="n">
         <v>1</v>
@@ -3175,8 +3072,10 @@
       <c r="G27" t="n">
         <v>10</v>
       </c>
-      <c r="H27" t="str">
-        <v>1,2,4,5</v>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>1,2,4,5</t>
+        </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -3186,7 +3085,7 @@
       <c r="J27" t="n">
         <v>2</v>
       </c>
-      <c r="K27" s="6" t="b">
+      <c r="K27" t="b">
         <v>1</v>
       </c>
       <c r="L27" t="inlineStr">
@@ -3200,7 +3099,7 @@
       <c r="N27" t="n">
         <v>2</v>
       </c>
-      <c r="O27" s="6" t="b">
+      <c r="O27" t="b">
         <v>0</v>
       </c>
       <c r="P27" t="inlineStr">
@@ -3208,21 +3107,26 @@
           <t>Growth</t>
         </is>
       </c>
-      <c r="Q27" t="str">
-        <v>3</v>
-      </c>
-      <c r="R27" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="S27" t="str">
-        <v>1,2,4,5</v>
-      </c>
-      <c r="T27" t="str">
-        <v>1,2,3,4,5,6,7,8,9,11</v>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R27" t="b">
+        <v>1</v>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>1,2,4,5</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,11</t>
+        </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="str"/>
       <c r="B28" t="n">
         <v>703</v>
       </c>
@@ -3232,8 +3136,10 @@
       <c r="D28" t="n">
         <v>400</v>
       </c>
-      <c r="E28" t="str">
-        <v>10,20,30</v>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>10,20,30</t>
+        </is>
       </c>
       <c r="F28" t="n">
         <v>1</v>
@@ -3241,8 +3147,10 @@
       <c r="G28" t="n">
         <v>10</v>
       </c>
-      <c r="H28" t="str">
-        <v>4</v>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -3252,17 +3160,16 @@
       <c r="J28" t="n">
         <v>2</v>
       </c>
-      <c r="K28" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="L28" t="str"/>
+      <c r="K28" t="b">
+        <v>1</v>
+      </c>
       <c r="M28" t="n">
         <v>1</v>
       </c>
       <c r="N28" t="n">
         <v>3</v>
       </c>
-      <c r="O28" s="6" t="b">
+      <c r="O28" t="b">
         <v>1</v>
       </c>
       <c r="P28" t="inlineStr">
@@ -3270,19 +3177,21 @@
           <t>Growth</t>
         </is>
       </c>
-      <c r="Q28" t="str"/>
-      <c r="R28" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="S28" t="str">
-        <v>1,2,4,5</v>
-      </c>
-      <c r="T28" t="str">
-        <v>1,2,3,4,5,6,7,8,9,11</v>
+      <c r="R28" t="b">
+        <v>1</v>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>1,2,4,5</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,11</t>
+        </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="str"/>
       <c r="B29" t="n">
         <v>801</v>
       </c>
@@ -3292,8 +3201,10 @@
       <c r="D29" t="n">
         <v>400</v>
       </c>
-      <c r="E29" t="str">
-        <v>10,20,30</v>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>10,20,30</t>
+        </is>
       </c>
       <c r="F29" t="n">
         <v>1</v>
@@ -3301,8 +3212,10 @@
       <c r="G29" t="n">
         <v>10</v>
       </c>
-      <c r="H29" t="str">
-        <v>1,2,4,5</v>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>1,2,4,5</t>
+        </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -3312,7 +3225,7 @@
       <c r="J29" t="n">
         <v>2</v>
       </c>
-      <c r="K29" s="6" t="b">
+      <c r="K29" t="b">
         <v>1</v>
       </c>
       <c r="L29" t="inlineStr">
@@ -3326,7 +3239,7 @@
       <c r="N29" t="n">
         <v>1</v>
       </c>
-      <c r="O29" s="6" t="b">
+      <c r="O29" t="b">
         <v>0</v>
       </c>
       <c r="P29" t="inlineStr">
@@ -3334,21 +3247,26 @@
           <t>Growth</t>
         </is>
       </c>
-      <c r="Q29" t="str">
-        <v>3</v>
-      </c>
-      <c r="R29" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="S29" t="str">
-        <v>1,2,4,5</v>
-      </c>
-      <c r="T29" t="str">
-        <v>1,2,3,4,5,6,7,8,9,11</v>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R29" t="b">
+        <v>1</v>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>1,2,4,5</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,11</t>
+        </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="str"/>
       <c r="B30" t="n">
         <v>802</v>
       </c>
@@ -3358,8 +3276,10 @@
       <c r="D30" t="n">
         <v>400</v>
       </c>
-      <c r="E30" t="str">
-        <v>10,20,30</v>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>10,20,30</t>
+        </is>
       </c>
       <c r="F30" t="n">
         <v>1</v>
@@ -3367,8 +3287,10 @@
       <c r="G30" t="n">
         <v>10</v>
       </c>
-      <c r="H30" t="str">
-        <v>1,2,4,5</v>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>1,2,4,5</t>
+        </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -3378,7 +3300,7 @@
       <c r="J30" t="n">
         <v>2</v>
       </c>
-      <c r="K30" s="6" t="b">
+      <c r="K30" t="b">
         <v>1</v>
       </c>
       <c r="L30" t="inlineStr">
@@ -3392,7 +3314,7 @@
       <c r="N30" t="n">
         <v>2</v>
       </c>
-      <c r="O30" s="6" t="b">
+      <c r="O30" t="b">
         <v>0</v>
       </c>
       <c r="P30" t="inlineStr">
@@ -3400,21 +3322,26 @@
           <t>Growth</t>
         </is>
       </c>
-      <c r="Q30" t="str">
-        <v>3</v>
-      </c>
-      <c r="R30" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="S30" t="str">
-        <v>1,2,4,5</v>
-      </c>
-      <c r="T30" t="str">
-        <v>1,2,3,4,5,6,7,8,9,11</v>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R30" t="b">
+        <v>1</v>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>1,2,4,5</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,11</t>
+        </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="str"/>
       <c r="B31" t="n">
         <v>803</v>
       </c>
@@ -3424,8 +3351,10 @@
       <c r="D31" t="n">
         <v>400</v>
       </c>
-      <c r="E31" t="str">
-        <v>10,20,30</v>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>10,20,30</t>
+        </is>
       </c>
       <c r="F31" t="n">
         <v>1</v>
@@ -3433,8 +3362,10 @@
       <c r="G31" t="n">
         <v>10</v>
       </c>
-      <c r="H31" t="str">
-        <v>4</v>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -3444,17 +3375,16 @@
       <c r="J31" t="n">
         <v>2</v>
       </c>
-      <c r="K31" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="L31" t="str"/>
+      <c r="K31" t="b">
+        <v>1</v>
+      </c>
       <c r="M31" t="n">
         <v>2</v>
       </c>
       <c r="N31" t="n">
         <v>3</v>
       </c>
-      <c r="O31" s="6" t="b">
+      <c r="O31" t="b">
         <v>1</v>
       </c>
       <c r="P31" t="inlineStr">
@@ -3462,19 +3392,21 @@
           <t>Growth</t>
         </is>
       </c>
-      <c r="Q31" t="str"/>
-      <c r="R31" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="S31" t="str">
-        <v>1,2,4,5</v>
-      </c>
-      <c r="T31" t="str">
-        <v>1,2,3,4,5,6,7,8,9,11</v>
+      <c r="R31" t="b">
+        <v>1</v>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>1,2,4,5</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,11</t>
+        </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="str"/>
       <c r="B32" t="n">
         <v>1101</v>
       </c>
@@ -3484,8 +3416,10 @@
       <c r="D32" t="n">
         <v>500</v>
       </c>
-      <c r="E32" t="str">
-        <v>10,20,30</v>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>10,20,30</t>
+        </is>
       </c>
       <c r="F32" t="n">
         <v>1</v>
@@ -3493,8 +3427,10 @@
       <c r="G32" t="n">
         <v>10</v>
       </c>
-      <c r="H32" t="str">
-        <v>1</v>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -3504,7 +3440,7 @@
       <c r="J32" t="n">
         <v>2</v>
       </c>
-      <c r="K32" s="6" t="b">
+      <c r="K32" t="b">
         <v>1</v>
       </c>
       <c r="L32" t="inlineStr">
@@ -3518,7 +3454,7 @@
       <c r="N32" t="n">
         <v>1</v>
       </c>
-      <c r="O32" s="6" t="b">
+      <c r="O32" t="b">
         <v>0</v>
       </c>
       <c r="P32" t="inlineStr">
@@ -3526,19 +3462,21 @@
           <t>Growth</t>
         </is>
       </c>
-      <c r="Q32" t="str"/>
-      <c r="R32" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="S32" t="str">
-        <v>1,2,4</v>
-      </c>
-      <c r="T32" t="str">
-        <v>1,2,3,4,5,6,7,8,9,11</v>
+      <c r="R32" t="b">
+        <v>1</v>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>1,2,4</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,11</t>
+        </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="str"/>
       <c r="B33" t="n">
         <v>1102</v>
       </c>
@@ -3548,8 +3486,10 @@
       <c r="D33" t="n">
         <v>650</v>
       </c>
-      <c r="E33" t="str">
-        <v>10,20,30</v>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>10,20,30</t>
+        </is>
       </c>
       <c r="F33" t="n">
         <v>1</v>
@@ -3557,8 +3497,10 @@
       <c r="G33" t="n">
         <v>10</v>
       </c>
-      <c r="H33" t="str">
-        <v>1,2</v>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>1,2</t>
+        </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -3568,7 +3510,7 @@
       <c r="J33" t="n">
         <v>2</v>
       </c>
-      <c r="K33" s="6" t="b">
+      <c r="K33" t="b">
         <v>1</v>
       </c>
       <c r="L33" t="inlineStr">
@@ -3582,7 +3524,7 @@
       <c r="N33" t="n">
         <v>2</v>
       </c>
-      <c r="O33" s="6" t="b">
+      <c r="O33" t="b">
         <v>0</v>
       </c>
       <c r="P33" t="inlineStr">
@@ -3590,19 +3532,21 @@
           <t>Growth</t>
         </is>
       </c>
-      <c r="Q33" t="str"/>
-      <c r="R33" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="S33" t="str">
-        <v>1,2,4</v>
-      </c>
-      <c r="T33" t="str">
-        <v>1,2,3,4,5,6,7,8,9,11</v>
+      <c r="R33" t="b">
+        <v>1</v>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>1,2,4</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,11</t>
+        </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="str"/>
       <c r="B34" t="n">
         <v>1103</v>
       </c>
@@ -3612,8 +3556,10 @@
       <c r="D34" t="n">
         <v>800</v>
       </c>
-      <c r="E34" t="str">
-        <v>10,20,30</v>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>10,20,30</t>
+        </is>
       </c>
       <c r="F34" t="n">
         <v>1</v>
@@ -3621,8 +3567,10 @@
       <c r="G34" t="n">
         <v>10</v>
       </c>
-      <c r="H34" t="str">
-        <v>1,2,4</v>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>1,2,4</t>
+        </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -3632,17 +3580,16 @@
       <c r="J34" t="n">
         <v>2</v>
       </c>
-      <c r="K34" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="L34" t="str"/>
+      <c r="K34" t="b">
+        <v>1</v>
+      </c>
       <c r="M34" t="n">
         <v>11</v>
       </c>
       <c r="N34" t="n">
         <v>3</v>
       </c>
-      <c r="O34" s="6" t="b">
+      <c r="O34" t="b">
         <v>1</v>
       </c>
       <c r="P34" t="inlineStr">
@@ -3650,19 +3597,21 @@
           <t>Growth</t>
         </is>
       </c>
-      <c r="Q34" t="str"/>
-      <c r="R34" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="S34" t="str">
-        <v>1,2,4</v>
-      </c>
-      <c r="T34" t="str">
-        <v>1,2,3,4,5,6,7,8,9,11</v>
+      <c r="R34" t="b">
+        <v>1</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>1,2,4</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,11</t>
+        </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="str"/>
       <c r="B35" t="n">
         <v>2101</v>
       </c>
@@ -3672,8 +3621,10 @@
       <c r="D35" t="n">
         <v>500</v>
       </c>
-      <c r="E35" t="str">
-        <v>10,20,30</v>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>10,20,30</t>
+        </is>
       </c>
       <c r="F35" t="n">
         <v>1</v>
@@ -3681,8 +3632,10 @@
       <c r="G35" t="n">
         <v>10</v>
       </c>
-      <c r="H35" t="str">
-        <v>1</v>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -3692,7 +3645,7 @@
       <c r="J35" t="n">
         <v>2</v>
       </c>
-      <c r="K35" s="6" t="b">
+      <c r="K35" t="b">
         <v>1</v>
       </c>
       <c r="L35" t="inlineStr">
@@ -3706,7 +3659,7 @@
       <c r="N35" t="n">
         <v>1</v>
       </c>
-      <c r="O35" s="6" t="b">
+      <c r="O35" t="b">
         <v>0</v>
       </c>
       <c r="P35" t="inlineStr">
@@ -3714,19 +3667,21 @@
           <t>Growth</t>
         </is>
       </c>
-      <c r="Q35" t="str"/>
-      <c r="R35" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="S35" t="str">
-        <v>1,2,4</v>
-      </c>
-      <c r="T35" t="str">
-        <v>1,2,3,4,5,6,7,8,9,11</v>
+      <c r="R35" t="b">
+        <v>1</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>1,2,4</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,11</t>
+        </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="str"/>
       <c r="B36" t="n">
         <v>2102</v>
       </c>
@@ -3736,8 +3691,10 @@
       <c r="D36" t="n">
         <v>650</v>
       </c>
-      <c r="E36" t="str">
-        <v>10,20,30</v>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>10,20,30</t>
+        </is>
       </c>
       <c r="F36" t="n">
         <v>1</v>
@@ -3745,8 +3702,10 @@
       <c r="G36" t="n">
         <v>10</v>
       </c>
-      <c r="H36" t="str">
-        <v>1,2</v>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>1,2</t>
+        </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -3756,7 +3715,7 @@
       <c r="J36" t="n">
         <v>2</v>
       </c>
-      <c r="K36" s="6" t="b">
+      <c r="K36" t="b">
         <v>1</v>
       </c>
       <c r="L36" t="inlineStr">
@@ -3770,7 +3729,7 @@
       <c r="N36" t="n">
         <v>2</v>
       </c>
-      <c r="O36" s="6" t="b">
+      <c r="O36" t="b">
         <v>0</v>
       </c>
       <c r="P36" t="inlineStr">
@@ -3778,19 +3737,21 @@
           <t>Growth</t>
         </is>
       </c>
-      <c r="Q36" t="str"/>
-      <c r="R36" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="S36" t="str">
-        <v>1,2,4</v>
-      </c>
-      <c r="T36" t="str">
-        <v>1,2,3,4,5,6,7,8,9,11</v>
+      <c r="R36" t="b">
+        <v>1</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>1,2,4</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,11</t>
+        </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="str"/>
       <c r="B37" t="n">
         <v>2103</v>
       </c>
@@ -3800,8 +3761,10 @@
       <c r="D37" t="n">
         <v>800</v>
       </c>
-      <c r="E37" t="str">
-        <v>10,20,30</v>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>10,20,30</t>
+        </is>
       </c>
       <c r="F37" t="n">
         <v>1</v>
@@ -3809,8 +3772,10 @@
       <c r="G37" t="n">
         <v>10</v>
       </c>
-      <c r="H37" t="str">
-        <v>1,2,4</v>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>1,2,4</t>
+        </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -3820,17 +3785,16 @@
       <c r="J37" t="n">
         <v>2</v>
       </c>
-      <c r="K37" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="L37" t="str"/>
+      <c r="K37" t="b">
+        <v>1</v>
+      </c>
       <c r="M37" t="n">
         <v>21</v>
       </c>
       <c r="N37" t="n">
         <v>3</v>
       </c>
-      <c r="O37" s="6" t="b">
+      <c r="O37" t="b">
         <v>1</v>
       </c>
       <c r="P37" t="inlineStr">
@@ -3838,19 +3802,21 @@
           <t>Growth</t>
         </is>
       </c>
-      <c r="Q37" t="str"/>
-      <c r="R37" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="S37" t="str">
-        <v>1,2,4</v>
-      </c>
-      <c r="T37" t="str">
-        <v>1,2,3,4,5,6,7,8,9,11</v>
+      <c r="R37" t="b">
+        <v>1</v>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>1,2,4</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,11</t>
+        </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="str"/>
       <c r="B38" t="n">
         <v>1201</v>
       </c>
@@ -3860,8 +3826,10 @@
       <c r="D38" t="n">
         <v>600</v>
       </c>
-      <c r="E38" t="str">
-        <v>10,20,30</v>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>10,20,30</t>
+        </is>
       </c>
       <c r="F38" t="n">
         <v>1</v>
@@ -3869,8 +3837,10 @@
       <c r="G38" t="n">
         <v>10</v>
       </c>
-      <c r="H38" t="str">
-        <v>4,5</v>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>4,5</t>
+        </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -3880,7 +3850,7 @@
       <c r="J38" t="n">
         <v>2</v>
       </c>
-      <c r="K38" s="6" t="b">
+      <c r="K38" t="b">
         <v>1</v>
       </c>
       <c r="L38" t="inlineStr">
@@ -3894,7 +3864,7 @@
       <c r="N38" t="n">
         <v>1</v>
       </c>
-      <c r="O38" s="6" t="b">
+      <c r="O38" t="b">
         <v>0</v>
       </c>
       <c r="P38" t="inlineStr">
@@ -3902,21 +3872,26 @@
           <t>Growth</t>
         </is>
       </c>
-      <c r="Q38" t="str">
-        <v>3</v>
-      </c>
-      <c r="R38" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="S38" t="str">
-        <v>1,2,3,4,5</v>
-      </c>
-      <c r="T38" t="str">
-        <v>1,2,3,4,5,6,7,8,9,10,11</v>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R38" t="b">
+        <v>1</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11</t>
+        </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="str"/>
       <c r="B39" t="n">
         <v>1202</v>
       </c>
@@ -3926,8 +3901,10 @@
       <c r="D39" t="n">
         <v>750</v>
       </c>
-      <c r="E39" t="str">
-        <v>10,20,30</v>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>10,20,30</t>
+        </is>
       </c>
       <c r="F39" t="n">
         <v>1</v>
@@ -3935,8 +3912,10 @@
       <c r="G39" t="n">
         <v>10</v>
       </c>
-      <c r="H39" t="str">
-        <v>1,4,5</v>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>1,4,5</t>
+        </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -3946,7 +3925,7 @@
       <c r="J39" t="n">
         <v>2</v>
       </c>
-      <c r="K39" s="6" t="b">
+      <c r="K39" t="b">
         <v>1</v>
       </c>
       <c r="L39" t="inlineStr">
@@ -3960,7 +3939,7 @@
       <c r="N39" t="n">
         <v>2</v>
       </c>
-      <c r="O39" s="6" t="b">
+      <c r="O39" t="b">
         <v>0</v>
       </c>
       <c r="P39" t="inlineStr">
@@ -3968,21 +3947,26 @@
           <t>Growth</t>
         </is>
       </c>
-      <c r="Q39" t="str">
-        <v>3</v>
-      </c>
-      <c r="R39" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="S39" t="str">
-        <v>1,2,3,4,5</v>
-      </c>
-      <c r="T39" t="str">
-        <v>1,2,3,4,5,6,7,8,9,10,11</v>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R39" t="b">
+        <v>1</v>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11</t>
+        </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="str"/>
       <c r="B40" t="n">
         <v>1203</v>
       </c>
@@ -3992,8 +3976,10 @@
       <c r="D40" t="n">
         <v>900</v>
       </c>
-      <c r="E40" t="str">
-        <v>10,20,30</v>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>10,20,30</t>
+        </is>
       </c>
       <c r="F40" t="n">
         <v>1</v>
@@ -4001,8 +3987,10 @@
       <c r="G40" t="n">
         <v>10</v>
       </c>
-      <c r="H40" t="str">
-        <v>1,2,4,5</v>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>1,2,4,5</t>
+        </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -4012,17 +4000,16 @@
       <c r="J40" t="n">
         <v>2</v>
       </c>
-      <c r="K40" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="L40" t="str"/>
+      <c r="K40" t="b">
+        <v>1</v>
+      </c>
       <c r="M40" t="n">
         <v>12</v>
       </c>
       <c r="N40" t="n">
         <v>3</v>
       </c>
-      <c r="O40" s="6" t="b">
+      <c r="O40" t="b">
         <v>1</v>
       </c>
       <c r="P40" t="inlineStr">
@@ -4030,21 +4017,26 @@
           <t>Growth</t>
         </is>
       </c>
-      <c r="Q40" t="str">
-        <v>3</v>
-      </c>
-      <c r="R40" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="S40" t="str">
-        <v>1,2,3,4,5</v>
-      </c>
-      <c r="T40" t="str">
-        <v>1,2,3,4,5,6,7,8,9,10,11</v>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R40" t="b">
+        <v>1</v>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11</t>
+        </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="str"/>
       <c r="B41" t="n">
         <v>2201</v>
       </c>
@@ -4054,8 +4046,10 @@
       <c r="D41" t="n">
         <v>600</v>
       </c>
-      <c r="E41" t="str">
-        <v>10,20,30</v>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>10,20,30</t>
+        </is>
       </c>
       <c r="F41" t="n">
         <v>1</v>
@@ -4063,8 +4057,10 @@
       <c r="G41" t="n">
         <v>10</v>
       </c>
-      <c r="H41" t="str">
-        <v>4,5</v>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>4,5</t>
+        </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -4074,7 +4070,7 @@
       <c r="J41" t="n">
         <v>2</v>
       </c>
-      <c r="K41" s="6" t="b">
+      <c r="K41" t="b">
         <v>1</v>
       </c>
       <c r="L41" t="inlineStr">
@@ -4088,7 +4084,7 @@
       <c r="N41" t="n">
         <v>1</v>
       </c>
-      <c r="O41" s="6" t="b">
+      <c r="O41" t="b">
         <v>0</v>
       </c>
       <c r="P41" t="inlineStr">
@@ -4096,21 +4092,26 @@
           <t>Growth</t>
         </is>
       </c>
-      <c r="Q41" t="str">
-        <v>3</v>
-      </c>
-      <c r="R41" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="S41" t="str">
-        <v>1,2,3,4,5</v>
-      </c>
-      <c r="T41" t="str">
-        <v>1,2,3,4,5,6,7,8,9,10,11</v>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R41" t="b">
+        <v>1</v>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11</t>
+        </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="str"/>
       <c r="B42" t="n">
         <v>2202</v>
       </c>
@@ -4120,8 +4121,10 @@
       <c r="D42" t="n">
         <v>750</v>
       </c>
-      <c r="E42" t="str">
-        <v>10,20,30</v>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>10,20,30</t>
+        </is>
       </c>
       <c r="F42" t="n">
         <v>1</v>
@@ -4129,8 +4132,10 @@
       <c r="G42" t="n">
         <v>10</v>
       </c>
-      <c r="H42" t="str">
-        <v>1,4,5</v>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>1,4,5</t>
+        </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -4140,7 +4145,7 @@
       <c r="J42" t="n">
         <v>2</v>
       </c>
-      <c r="K42" s="6" t="b">
+      <c r="K42" t="b">
         <v>1</v>
       </c>
       <c r="L42" t="inlineStr">
@@ -4154,7 +4159,7 @@
       <c r="N42" t="n">
         <v>2</v>
       </c>
-      <c r="O42" s="6" t="b">
+      <c r="O42" t="b">
         <v>0</v>
       </c>
       <c r="P42" t="inlineStr">
@@ -4162,21 +4167,26 @@
           <t>Growth</t>
         </is>
       </c>
-      <c r="Q42" t="str">
-        <v>3</v>
-      </c>
-      <c r="R42" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="S42" t="str">
-        <v>1,2,3,4,5</v>
-      </c>
-      <c r="T42" t="str">
-        <v>1,2,3,4,5,6,7,8,9,10,11</v>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R42" t="b">
+        <v>1</v>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11</t>
+        </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="str"/>
       <c r="B43" t="n">
         <v>2203</v>
       </c>
@@ -4186,8 +4196,10 @@
       <c r="D43" t="n">
         <v>900</v>
       </c>
-      <c r="E43" t="str">
-        <v>10,20,30</v>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>10,20,30</t>
+        </is>
       </c>
       <c r="F43" t="n">
         <v>1</v>
@@ -4195,8 +4207,10 @@
       <c r="G43" t="n">
         <v>10</v>
       </c>
-      <c r="H43" t="str">
-        <v>1,2,4,5</v>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>1,2,4,5</t>
+        </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -4206,17 +4220,16 @@
       <c r="J43" t="n">
         <v>2</v>
       </c>
-      <c r="K43" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="L43" t="str"/>
+      <c r="K43" t="b">
+        <v>1</v>
+      </c>
       <c r="M43" t="n">
         <v>22</v>
       </c>
       <c r="N43" t="n">
         <v>3</v>
       </c>
-      <c r="O43" s="6" t="b">
+      <c r="O43" t="b">
         <v>1</v>
       </c>
       <c r="P43" t="inlineStr">
@@ -4224,21 +4237,26 @@
           <t>Growth</t>
         </is>
       </c>
-      <c r="Q43" t="str">
-        <v>3</v>
-      </c>
-      <c r="R43" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="S43" t="str">
-        <v>1,2,3,4,5</v>
-      </c>
-      <c r="T43" t="str">
-        <v>1,2,3,4,5,6,7,8,9,10,11</v>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R43" t="b">
+        <v>1</v>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11</t>
+        </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="str"/>
       <c r="B44" t="n">
         <v>901</v>
       </c>
@@ -4248,8 +4266,10 @@
       <c r="D44" t="n">
         <v>900</v>
       </c>
-      <c r="E44" t="str">
-        <v>10,20,30</v>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>10,20,30</t>
+        </is>
       </c>
       <c r="F44" t="n">
         <v>1</v>
@@ -4257,8 +4277,10 @@
       <c r="G44" t="n">
         <v>10</v>
       </c>
-      <c r="H44" t="str">
-        <v>6,7</v>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>6,7</t>
+        </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -4268,7 +4290,7 @@
       <c r="J44" t="n">
         <v>2</v>
       </c>
-      <c r="K44" s="6" t="b">
+      <c r="K44" t="b">
         <v>1</v>
       </c>
       <c r="L44" t="inlineStr">
@@ -4282,7 +4304,7 @@
       <c r="N44" t="n">
         <v>1</v>
       </c>
-      <c r="O44" s="6" t="b">
+      <c r="O44" t="b">
         <v>0</v>
       </c>
       <c r="P44" t="inlineStr">
@@ -4290,19 +4312,21 @@
           <t>Hot</t>
         </is>
       </c>
-      <c r="Q44" t="str"/>
-      <c r="R44" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="S44" t="str">
-        <v>6,7</v>
-      </c>
-      <c r="T44" t="str">
-        <v>1,2,3,4,5,6,7,8,9,10,11,12</v>
+      <c r="R44" t="b">
+        <v>1</v>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>6,7</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11,12</t>
+        </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="str"/>
       <c r="B45" t="n">
         <v>902</v>
       </c>
@@ -4312,8 +4336,10 @@
       <c r="D45" t="n">
         <v>1000</v>
       </c>
-      <c r="E45" t="str">
-        <v>10,20,30</v>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>10,20,30</t>
+        </is>
       </c>
       <c r="F45" t="n">
         <v>1</v>
@@ -4321,8 +4347,10 @@
       <c r="G45" t="n">
         <v>10</v>
       </c>
-      <c r="H45" t="str">
-        <v>6,7</v>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>6,7</t>
+        </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -4332,7 +4360,7 @@
       <c r="J45" t="n">
         <v>2</v>
       </c>
-      <c r="K45" s="6" t="b">
+      <c r="K45" t="b">
         <v>1</v>
       </c>
       <c r="L45" t="inlineStr">
@@ -4346,7 +4374,7 @@
       <c r="N45" t="n">
         <v>2</v>
       </c>
-      <c r="O45" s="6" t="b">
+      <c r="O45" t="b">
         <v>0</v>
       </c>
       <c r="P45" t="inlineStr">
@@ -4354,19 +4382,21 @@
           <t>Hot</t>
         </is>
       </c>
-      <c r="Q45" t="str"/>
-      <c r="R45" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="S45" t="str">
-        <v>6,7</v>
-      </c>
-      <c r="T45" t="str">
-        <v>1,2,3,4,5,6,7,8,9,10,11,12</v>
+      <c r="R45" t="b">
+        <v>1</v>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>6,7</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11,12</t>
+        </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="str"/>
       <c r="B46" t="n">
         <v>903</v>
       </c>
@@ -4376,8 +4406,10 @@
       <c r="D46" t="n">
         <v>1100</v>
       </c>
-      <c r="E46" t="str">
-        <v>10,20,30</v>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>10,20,30</t>
+        </is>
       </c>
       <c r="F46" t="n">
         <v>1</v>
@@ -4385,8 +4417,10 @@
       <c r="G46" t="n">
         <v>10</v>
       </c>
-      <c r="H46" t="str">
-        <v>6,7</v>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>6,7</t>
+        </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -4396,17 +4430,16 @@
       <c r="J46" t="n">
         <v>2</v>
       </c>
-      <c r="K46" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="L46" t="str"/>
+      <c r="K46" t="b">
+        <v>1</v>
+      </c>
       <c r="M46" t="n">
         <v>1</v>
       </c>
       <c r="N46" t="n">
         <v>3</v>
       </c>
-      <c r="O46" s="6" t="b">
+      <c r="O46" t="b">
         <v>1</v>
       </c>
       <c r="P46" t="inlineStr">
@@ -4414,19 +4447,21 @@
           <t>Hot</t>
         </is>
       </c>
-      <c r="Q46" t="str"/>
-      <c r="R46" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="S46" t="str">
-        <v>6,7</v>
-      </c>
-      <c r="T46" t="str">
-        <v>1,2,3,4,5,6,7,8,9,10,11,12</v>
+      <c r="R46" t="b">
+        <v>1</v>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>6,7</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11,12</t>
+        </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="str"/>
       <c r="B47" t="n">
         <v>1001</v>
       </c>
@@ -4436,8 +4471,10 @@
       <c r="D47" t="n">
         <v>900</v>
       </c>
-      <c r="E47" t="str">
-        <v>10,20,30</v>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>10,20,30</t>
+        </is>
       </c>
       <c r="F47" t="n">
         <v>1</v>
@@ -4445,8 +4482,10 @@
       <c r="G47" t="n">
         <v>10</v>
       </c>
-      <c r="H47" t="str">
-        <v>6,7</v>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>6,7</t>
+        </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -4456,7 +4495,7 @@
       <c r="J47" t="n">
         <v>2</v>
       </c>
-      <c r="K47" s="6" t="b">
+      <c r="K47" t="b">
         <v>1</v>
       </c>
       <c r="L47" t="inlineStr">
@@ -4470,7 +4509,7 @@
       <c r="N47" t="n">
         <v>1</v>
       </c>
-      <c r="O47" s="6" t="b">
+      <c r="O47" t="b">
         <v>0</v>
       </c>
       <c r="P47" t="inlineStr">
@@ -4478,19 +4517,21 @@
           <t>Hot</t>
         </is>
       </c>
-      <c r="Q47" t="str"/>
-      <c r="R47" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="S47" t="str">
-        <v>6,7</v>
-      </c>
-      <c r="T47" t="str">
-        <v>1,2,3,4,5,6,7,8,9,10,11,12</v>
+      <c r="R47" t="b">
+        <v>1</v>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>6,7</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11,12</t>
+        </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="str"/>
       <c r="B48" t="n">
         <v>1002</v>
       </c>
@@ -4500,8 +4541,10 @@
       <c r="D48" t="n">
         <v>1000</v>
       </c>
-      <c r="E48" t="str">
-        <v>10,20,30</v>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>10,20,30</t>
+        </is>
       </c>
       <c r="F48" t="n">
         <v>1</v>
@@ -4509,8 +4552,10 @@
       <c r="G48" t="n">
         <v>10</v>
       </c>
-      <c r="H48" t="str">
-        <v>6,7</v>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>6,7</t>
+        </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -4520,7 +4565,7 @@
       <c r="J48" t="n">
         <v>2</v>
       </c>
-      <c r="K48" s="6" t="b">
+      <c r="K48" t="b">
         <v>1</v>
       </c>
       <c r="L48" t="inlineStr">
@@ -4534,7 +4579,7 @@
       <c r="N48" t="n">
         <v>2</v>
       </c>
-      <c r="O48" s="6" t="b">
+      <c r="O48" t="b">
         <v>0</v>
       </c>
       <c r="P48" t="inlineStr">
@@ -4542,19 +4587,21 @@
           <t>Hot</t>
         </is>
       </c>
-      <c r="Q48" t="str"/>
-      <c r="R48" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="S48" t="str">
-        <v>6,7</v>
-      </c>
-      <c r="T48" t="str">
-        <v>1,2,3,4,5,6,7,8,9,10,11,12</v>
+      <c r="R48" t="b">
+        <v>1</v>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>6,7</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11,12</t>
+        </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="str"/>
       <c r="B49" t="n">
         <v>1003</v>
       </c>
@@ -4564,8 +4611,10 @@
       <c r="D49" t="n">
         <v>1100</v>
       </c>
-      <c r="E49" t="str">
-        <v>10,20,30</v>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>10,20,30</t>
+        </is>
       </c>
       <c r="F49" t="n">
         <v>1</v>
@@ -4573,8 +4622,10 @@
       <c r="G49" t="n">
         <v>10</v>
       </c>
-      <c r="H49" t="str">
-        <v>6,7</v>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>6,7</t>
+        </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -4584,17 +4635,16 @@
       <c r="J49" t="n">
         <v>2</v>
       </c>
-      <c r="K49" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="L49" t="str"/>
+      <c r="K49" t="b">
+        <v>1</v>
+      </c>
       <c r="M49" t="n">
         <v>2</v>
       </c>
       <c r="N49" t="n">
         <v>3</v>
       </c>
-      <c r="O49" s="6" t="b">
+      <c r="O49" t="b">
         <v>1</v>
       </c>
       <c r="P49" t="inlineStr">
@@ -4602,19 +4652,21 @@
           <t>Hot</t>
         </is>
       </c>
-      <c r="Q49" t="str"/>
-      <c r="R49" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="S49" t="str">
-        <v>6,7</v>
-      </c>
-      <c r="T49" t="str">
-        <v>1,2,3,4,5,6,7,8,9,10,11,12</v>
+      <c r="R49" t="b">
+        <v>1</v>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>6,7</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11,12</t>
+        </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="str"/>
       <c r="B50" t="n">
         <v>1301</v>
       </c>
@@ -4624,8 +4676,10 @@
       <c r="D50" t="n">
         <v>900</v>
       </c>
-      <c r="E50" t="str">
-        <v>10,20,30</v>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>10,20,30</t>
+        </is>
       </c>
       <c r="F50" t="n">
         <v>1</v>
@@ -4633,8 +4687,10 @@
       <c r="G50" t="n">
         <v>10</v>
       </c>
-      <c r="H50" t="str">
-        <v>8</v>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -4644,7 +4700,7 @@
       <c r="J50" t="n">
         <v>2</v>
       </c>
-      <c r="K50" s="6" t="b">
+      <c r="K50" t="b">
         <v>1</v>
       </c>
       <c r="L50" t="inlineStr">
@@ -4658,7 +4714,7 @@
       <c r="N50" t="n">
         <v>1</v>
       </c>
-      <c r="O50" s="6" t="b">
+      <c r="O50" t="b">
         <v>0</v>
       </c>
       <c r="P50" t="inlineStr">
@@ -4666,19 +4722,21 @@
           <t>Dessert</t>
         </is>
       </c>
-      <c r="Q50" t="str"/>
-      <c r="R50" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="S50" t="str">
-        <v>8</v>
-      </c>
-      <c r="T50" t="str">
-        <v>1,2,3,4,5,6,7,8,9,13</v>
+      <c r="R50" t="b">
+        <v>1</v>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,13</t>
+        </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="str"/>
       <c r="B51" t="n">
         <v>1302</v>
       </c>
@@ -4688,8 +4746,10 @@
       <c r="D51" t="n">
         <v>1000</v>
       </c>
-      <c r="E51" t="str">
-        <v>10,20,30</v>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>10,20,30</t>
+        </is>
       </c>
       <c r="F51" t="n">
         <v>1</v>
@@ -4697,8 +4757,10 @@
       <c r="G51" t="n">
         <v>10</v>
       </c>
-      <c r="H51" t="str">
-        <v>8</v>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -4708,7 +4770,7 @@
       <c r="J51" t="n">
         <v>2</v>
       </c>
-      <c r="K51" s="6" t="b">
+      <c r="K51" t="b">
         <v>1</v>
       </c>
       <c r="L51" t="inlineStr">
@@ -4722,7 +4784,7 @@
       <c r="N51" t="n">
         <v>2</v>
       </c>
-      <c r="O51" s="6" t="b">
+      <c r="O51" t="b">
         <v>0</v>
       </c>
       <c r="P51" t="inlineStr">
@@ -4730,19 +4792,21 @@
           <t>Dessert</t>
         </is>
       </c>
-      <c r="Q51" t="str"/>
-      <c r="R51" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="S51" t="str">
-        <v>8</v>
-      </c>
-      <c r="T51" t="str">
-        <v>1,2,3,4,5,6,7,8,9,13</v>
+      <c r="R51" t="b">
+        <v>1</v>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,13</t>
+        </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="str"/>
       <c r="B52" t="n">
         <v>1303</v>
       </c>
@@ -4752,8 +4816,10 @@
       <c r="D52" t="n">
         <v>1100</v>
       </c>
-      <c r="E52" t="str">
-        <v>10,20,30</v>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>10,20,30</t>
+        </is>
       </c>
       <c r="F52" t="n">
         <v>1</v>
@@ -4761,8 +4827,10 @@
       <c r="G52" t="n">
         <v>10</v>
       </c>
-      <c r="H52" t="str">
-        <v>8</v>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -4772,17 +4840,16 @@
       <c r="J52" t="n">
         <v>2</v>
       </c>
-      <c r="K52" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="L52" t="str"/>
+      <c r="K52" t="b">
+        <v>1</v>
+      </c>
       <c r="M52" t="n">
         <v>1</v>
       </c>
       <c r="N52" t="n">
         <v>3</v>
       </c>
-      <c r="O52" s="6" t="b">
+      <c r="O52" t="b">
         <v>1</v>
       </c>
       <c r="P52" t="inlineStr">
@@ -4790,19 +4857,21 @@
           <t>Dessert</t>
         </is>
       </c>
-      <c r="Q52" t="str"/>
-      <c r="R52" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="S52" t="str">
-        <v>8</v>
-      </c>
-      <c r="T52" t="str">
-        <v>1,2,3,4,5,6,7,8,9,13</v>
+      <c r="R52" t="b">
+        <v>1</v>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,13</t>
+        </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="str"/>
       <c r="B53" t="n">
         <v>2301</v>
       </c>
@@ -4812,8 +4881,10 @@
       <c r="D53" t="n">
         <v>900</v>
       </c>
-      <c r="E53" t="str">
-        <v>10,20,30</v>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>10,20,30</t>
+        </is>
       </c>
       <c r="F53" t="n">
         <v>1</v>
@@ -4821,8 +4892,10 @@
       <c r="G53" t="n">
         <v>10</v>
       </c>
-      <c r="H53" t="str">
-        <v>8</v>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -4832,7 +4905,7 @@
       <c r="J53" t="n">
         <v>2</v>
       </c>
-      <c r="K53" s="6" t="b">
+      <c r="K53" t="b">
         <v>1</v>
       </c>
       <c r="L53" t="inlineStr">
@@ -4846,7 +4919,7 @@
       <c r="N53" t="n">
         <v>1</v>
       </c>
-      <c r="O53" s="6" t="b">
+      <c r="O53" t="b">
         <v>0</v>
       </c>
       <c r="P53" t="inlineStr">
@@ -4854,19 +4927,21 @@
           <t>Dessert</t>
         </is>
       </c>
-      <c r="Q53" t="str"/>
-      <c r="R53" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="S53" t="str">
-        <v>8</v>
-      </c>
-      <c r="T53" t="str">
-        <v>1,2,3,4,5,6,7,8,9,13</v>
+      <c r="R53" t="b">
+        <v>1</v>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,13</t>
+        </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="str"/>
       <c r="B54" t="n">
         <v>2302</v>
       </c>
@@ -4876,8 +4951,10 @@
       <c r="D54" t="n">
         <v>1000</v>
       </c>
-      <c r="E54" t="str">
-        <v>10,20,30</v>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>10,20,30</t>
+        </is>
       </c>
       <c r="F54" t="n">
         <v>1</v>
@@ -4885,8 +4962,10 @@
       <c r="G54" t="n">
         <v>10</v>
       </c>
-      <c r="H54" t="str">
-        <v>8</v>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -4896,7 +4975,7 @@
       <c r="J54" t="n">
         <v>2</v>
       </c>
-      <c r="K54" s="6" t="b">
+      <c r="K54" t="b">
         <v>1</v>
       </c>
       <c r="L54" t="inlineStr">
@@ -4910,7 +4989,7 @@
       <c r="N54" t="n">
         <v>2</v>
       </c>
-      <c r="O54" s="6" t="b">
+      <c r="O54" t="b">
         <v>0</v>
       </c>
       <c r="P54" t="inlineStr">
@@ -4918,19 +4997,21 @@
           <t>Dessert</t>
         </is>
       </c>
-      <c r="Q54" t="str"/>
-      <c r="R54" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="S54" t="str">
-        <v>8</v>
-      </c>
-      <c r="T54" t="str">
-        <v>1,2,3,4,5,6,7,8,9,13</v>
+      <c r="R54" t="b">
+        <v>1</v>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,13</t>
+        </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="str"/>
       <c r="B55" t="n">
         <v>2303</v>
       </c>
@@ -4940,8 +5021,10 @@
       <c r="D55" t="n">
         <v>1100</v>
       </c>
-      <c r="E55" t="str">
-        <v>10,20,30</v>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>10,20,30</t>
+        </is>
       </c>
       <c r="F55" t="n">
         <v>1</v>
@@ -4949,8 +5032,10 @@
       <c r="G55" t="n">
         <v>10</v>
       </c>
-      <c r="H55" t="str">
-        <v>8</v>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -4960,17 +5045,16 @@
       <c r="J55" t="n">
         <v>2</v>
       </c>
-      <c r="K55" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="L55" t="str"/>
+      <c r="K55" t="b">
+        <v>1</v>
+      </c>
       <c r="M55" t="n">
         <v>2</v>
       </c>
       <c r="N55" t="n">
         <v>3</v>
       </c>
-      <c r="O55" s="6" t="b">
+      <c r="O55" t="b">
         <v>1</v>
       </c>
       <c r="P55" t="inlineStr">
@@ -4978,19 +5062,21 @@
           <t>Dessert</t>
         </is>
       </c>
-      <c r="Q55" t="str"/>
-      <c r="R55" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="S55" t="str">
-        <v>8</v>
-      </c>
-      <c r="T55" t="str">
-        <v>1,2,3,4,5,6,7,8,9,13</v>
+      <c r="R55" t="b">
+        <v>1</v>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,13</t>
+        </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="str"/>
       <c r="B56" t="n">
         <v>1401</v>
       </c>
@@ -5000,8 +5086,10 @@
       <c r="D56" t="n">
         <v>900</v>
       </c>
-      <c r="E56" t="str">
-        <v>10,20,30</v>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>10,20,30</t>
+        </is>
       </c>
       <c r="F56" t="n">
         <v>1</v>
@@ -5009,7 +5097,6 @@
       <c r="G56" t="n">
         <v>10</v>
       </c>
-      <c r="H56" t="str"/>
       <c r="I56" t="inlineStr">
         <is>
           <t>15,16,17,18</t>
@@ -5018,7 +5105,7 @@
       <c r="J56" t="n">
         <v>2</v>
       </c>
-      <c r="K56" s="6" t="b">
+      <c r="K56" t="b">
         <v>1</v>
       </c>
       <c r="L56" t="inlineStr">
@@ -5032,7 +5119,7 @@
       <c r="N56" t="n">
         <v>1</v>
       </c>
-      <c r="O56" s="6" t="b">
+      <c r="O56" t="b">
         <v>0</v>
       </c>
       <c r="P56" t="inlineStr">
@@ -5040,21 +5127,26 @@
           <t>Cafe</t>
         </is>
       </c>
-      <c r="Q56" t="str">
-        <v>9,10,11</v>
-      </c>
-      <c r="R56" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="S56" t="str">
-        <v>1,2,3,4,5,6,7,8,9,10,11</v>
-      </c>
-      <c r="T56" t="str">
-        <v>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16</v>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>9,10,11</t>
+        </is>
+      </c>
+      <c r="R56" t="b">
+        <v>1</v>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16</t>
+        </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="str"/>
       <c r="B57" t="n">
         <v>1402</v>
       </c>
@@ -5064,8 +5156,10 @@
       <c r="D57" t="n">
         <v>1000</v>
       </c>
-      <c r="E57" t="str">
-        <v>10,20,30</v>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>10,20,30</t>
+        </is>
       </c>
       <c r="F57" t="n">
         <v>1</v>
@@ -5073,7 +5167,6 @@
       <c r="G57" t="n">
         <v>10</v>
       </c>
-      <c r="H57" t="str"/>
       <c r="I57" t="inlineStr">
         <is>
           <t>15,16,17,18</t>
@@ -5082,7 +5175,7 @@
       <c r="J57" t="n">
         <v>2</v>
       </c>
-      <c r="K57" s="6" t="b">
+      <c r="K57" t="b">
         <v>1</v>
       </c>
       <c r="L57" t="inlineStr">
@@ -5096,7 +5189,7 @@
       <c r="N57" t="n">
         <v>2</v>
       </c>
-      <c r="O57" s="6" t="b">
+      <c r="O57" t="b">
         <v>0</v>
       </c>
       <c r="P57" t="inlineStr">
@@ -5104,21 +5197,26 @@
           <t>Cafe</t>
         </is>
       </c>
-      <c r="Q57" t="str">
-        <v>9,10,11</v>
-      </c>
-      <c r="R57" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="S57" t="str">
-        <v>1,2,3,4,5,6,7,8,9,10,11</v>
-      </c>
-      <c r="T57" t="str">
-        <v>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16</v>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>9,10,11</t>
+        </is>
+      </c>
+      <c r="R57" t="b">
+        <v>1</v>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16</t>
+        </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="str"/>
       <c r="B58" t="n">
         <v>1403</v>
       </c>
@@ -5128,8 +5226,10 @@
       <c r="D58" t="n">
         <v>1100</v>
       </c>
-      <c r="E58" t="str">
-        <v>10,20,30</v>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>10,20,30</t>
+        </is>
       </c>
       <c r="F58" t="n">
         <v>1</v>
@@ -5137,7 +5237,6 @@
       <c r="G58" t="n">
         <v>10</v>
       </c>
-      <c r="H58" t="str"/>
       <c r="I58" t="inlineStr">
         <is>
           <t>15,16,17,18</t>
@@ -5146,17 +5245,16 @@
       <c r="J58" t="n">
         <v>2</v>
       </c>
-      <c r="K58" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="L58" t="str"/>
+      <c r="K58" t="b">
+        <v>1</v>
+      </c>
       <c r="M58" t="n">
         <v>1</v>
       </c>
       <c r="N58" t="n">
         <v>3</v>
       </c>
-      <c r="O58" s="6" t="b">
+      <c r="O58" t="b">
         <v>1</v>
       </c>
       <c r="P58" t="inlineStr">
@@ -5164,21 +5262,26 @@
           <t>Cafe</t>
         </is>
       </c>
-      <c r="Q58" t="str">
-        <v>9,10,11</v>
-      </c>
-      <c r="R58" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="S58" t="str">
-        <v>1,2,3,4,5,6,7,8,9,10,11</v>
-      </c>
-      <c r="T58" t="str">
-        <v>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16</v>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>9,10,11</t>
+        </is>
+      </c>
+      <c r="R58" t="b">
+        <v>1</v>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16</t>
+        </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="str"/>
       <c r="B59" t="n">
         <v>2401</v>
       </c>
@@ -5188,8 +5291,10 @@
       <c r="D59" t="n">
         <v>900</v>
       </c>
-      <c r="E59" t="str">
-        <v>10,20,30</v>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>10,20,30</t>
+        </is>
       </c>
       <c r="F59" t="n">
         <v>1</v>
@@ -5197,7 +5302,6 @@
       <c r="G59" t="n">
         <v>10</v>
       </c>
-      <c r="H59" t="str"/>
       <c r="I59" t="inlineStr">
         <is>
           <t>15,16,17,18</t>
@@ -5206,7 +5310,7 @@
       <c r="J59" t="n">
         <v>2</v>
       </c>
-      <c r="K59" s="6" t="b">
+      <c r="K59" t="b">
         <v>1</v>
       </c>
       <c r="L59" t="inlineStr">
@@ -5220,7 +5324,7 @@
       <c r="N59" t="n">
         <v>1</v>
       </c>
-      <c r="O59" s="6" t="b">
+      <c r="O59" t="b">
         <v>0</v>
       </c>
       <c r="P59" t="inlineStr">
@@ -5228,21 +5332,26 @@
           <t>Cafe</t>
         </is>
       </c>
-      <c r="Q59" t="str">
-        <v>9,10,11</v>
-      </c>
-      <c r="R59" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="S59" t="str">
-        <v>1,2,3,4,5,6,7,8,9,10,11</v>
-      </c>
-      <c r="T59" t="str">
-        <v>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16</v>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>9,10,11</t>
+        </is>
+      </c>
+      <c r="R59" t="b">
+        <v>1</v>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16</t>
+        </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="str"/>
       <c r="B60" t="n">
         <v>2402</v>
       </c>
@@ -5252,8 +5361,10 @@
       <c r="D60" t="n">
         <v>1000</v>
       </c>
-      <c r="E60" t="str">
-        <v>10,20,30</v>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>10,20,30</t>
+        </is>
       </c>
       <c r="F60" t="n">
         <v>1</v>
@@ -5261,7 +5372,6 @@
       <c r="G60" t="n">
         <v>10</v>
       </c>
-      <c r="H60" t="str"/>
       <c r="I60" t="inlineStr">
         <is>
           <t>15,16,17,18</t>
@@ -5270,7 +5380,7 @@
       <c r="J60" t="n">
         <v>2</v>
       </c>
-      <c r="K60" s="6" t="b">
+      <c r="K60" t="b">
         <v>1</v>
       </c>
       <c r="L60" t="inlineStr">
@@ -5284,7 +5394,7 @@
       <c r="N60" t="n">
         <v>2</v>
       </c>
-      <c r="O60" s="6" t="b">
+      <c r="O60" t="b">
         <v>0</v>
       </c>
       <c r="P60" t="inlineStr">
@@ -5292,21 +5402,26 @@
           <t>Cafe</t>
         </is>
       </c>
-      <c r="Q60" t="str">
-        <v>9,10,11</v>
-      </c>
-      <c r="R60" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="S60" t="str">
-        <v>1,2,3,4,5,6,7,8,9,10,11</v>
-      </c>
-      <c r="T60" t="str">
-        <v>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16</v>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>9,10,11</t>
+        </is>
+      </c>
+      <c r="R60" t="b">
+        <v>1</v>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16</t>
+        </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="str"/>
       <c r="B61" t="n">
         <v>2403</v>
       </c>
@@ -5316,8 +5431,10 @@
       <c r="D61" t="n">
         <v>1100</v>
       </c>
-      <c r="E61" t="str">
-        <v>10,20,30</v>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>10,20,30</t>
+        </is>
       </c>
       <c r="F61" t="n">
         <v>1</v>
@@ -5325,7 +5442,6 @@
       <c r="G61" t="n">
         <v>10</v>
       </c>
-      <c r="H61" t="str"/>
       <c r="I61" t="inlineStr">
         <is>
           <t>15,16,17,18</t>
@@ -5334,17 +5450,16 @@
       <c r="J61" t="n">
         <v>2</v>
       </c>
-      <c r="K61" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="L61" t="str"/>
+      <c r="K61" t="b">
+        <v>1</v>
+      </c>
       <c r="M61" t="n">
         <v>2</v>
       </c>
       <c r="N61" t="n">
         <v>3</v>
       </c>
-      <c r="O61" s="6" t="b">
+      <c r="O61" t="b">
         <v>1</v>
       </c>
       <c r="P61" t="inlineStr">
@@ -5352,21 +5467,26 @@
           <t>Cafe</t>
         </is>
       </c>
-      <c r="Q61" t="str">
-        <v>9,10,11</v>
-      </c>
-      <c r="R61" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="S61" t="str">
-        <v>1,2,3,4,5,6,7,8,9,10,11</v>
-      </c>
-      <c r="T61" t="str">
-        <v>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16</v>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>9,10,11</t>
+        </is>
+      </c>
+      <c r="R61" t="b">
+        <v>1</v>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16</t>
+        </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="str"/>
       <c r="B62" t="n">
         <v>1501</v>
       </c>
@@ -5376,8 +5496,10 @@
       <c r="D62" t="n">
         <v>600</v>
       </c>
-      <c r="E62" t="str">
-        <v>10,20,30</v>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>10,20,30</t>
+        </is>
       </c>
       <c r="F62" t="n">
         <v>1</v>
@@ -5385,8 +5507,10 @@
       <c r="G62" t="n">
         <v>10</v>
       </c>
-      <c r="H62" t="str">
-        <v>4,5,6</v>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>4,5,6</t>
+        </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -5396,7 +5520,7 @@
       <c r="J62" t="n">
         <v>2</v>
       </c>
-      <c r="K62" s="6" t="b">
+      <c r="K62" t="b">
         <v>1</v>
       </c>
       <c r="L62" t="inlineStr">
@@ -5410,7 +5534,7 @@
       <c r="N62" t="n">
         <v>1</v>
       </c>
-      <c r="O62" s="6" t="b">
+      <c r="O62" t="b">
         <v>0</v>
       </c>
       <c r="P62" t="inlineStr">
@@ -5418,21 +5542,26 @@
           <t>Cafe</t>
         </is>
       </c>
-      <c r="Q62" t="str">
-        <v>3,9</v>
-      </c>
-      <c r="R62" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="S62" t="str">
-        <v>1,2,3,4,5,6,7,8,9,10,11</v>
-      </c>
-      <c r="T62" t="str">
-        <v>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16</v>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>3,9</t>
+        </is>
+      </c>
+      <c r="R62" t="b">
+        <v>1</v>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16</t>
+        </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="str"/>
       <c r="B63" t="n">
         <v>1502</v>
       </c>
@@ -5442,8 +5571,10 @@
       <c r="D63" t="n">
         <v>750</v>
       </c>
-      <c r="E63" t="str">
-        <v>10,20,30</v>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>10,20,30</t>
+        </is>
       </c>
       <c r="F63" t="n">
         <v>1</v>
@@ -5451,8 +5582,10 @@
       <c r="G63" t="n">
         <v>10</v>
       </c>
-      <c r="H63" t="str">
-        <v>1,4,5,6,7,8</v>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>1,4,5,6,7,8</t>
+        </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -5462,7 +5595,7 @@
       <c r="J63" t="n">
         <v>2</v>
       </c>
-      <c r="K63" s="6" t="b">
+      <c r="K63" t="b">
         <v>1</v>
       </c>
       <c r="L63" t="inlineStr">
@@ -5476,7 +5609,7 @@
       <c r="N63" t="n">
         <v>2</v>
       </c>
-      <c r="O63" s="6" t="b">
+      <c r="O63" t="b">
         <v>0</v>
       </c>
       <c r="P63" t="inlineStr">
@@ -5484,21 +5617,26 @@
           <t>Cafe</t>
         </is>
       </c>
-      <c r="Q63" t="str">
-        <v>3,9,10</v>
-      </c>
-      <c r="R63" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="S63" t="str">
-        <v>1,2,3,4,5,6,7,8,9,10,11</v>
-      </c>
-      <c r="T63" t="str">
-        <v>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16</v>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>3,9,10</t>
+        </is>
+      </c>
+      <c r="R63" t="b">
+        <v>1</v>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16</t>
+        </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="str"/>
       <c r="B64" t="n">
         <v>1503</v>
       </c>
@@ -5508,8 +5646,10 @@
       <c r="D64" t="n">
         <v>900</v>
       </c>
-      <c r="E64" t="str">
-        <v>10,20,30</v>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>10,20,30</t>
+        </is>
       </c>
       <c r="F64" t="n">
         <v>1</v>
@@ -5517,8 +5657,10 @@
       <c r="G64" t="n">
         <v>10</v>
       </c>
-      <c r="H64" t="str">
-        <v>1,2,4,5,6,7,8</v>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>1,2,4,5,6,7,8</t>
+        </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -5528,17 +5670,16 @@
       <c r="J64" t="n">
         <v>2</v>
       </c>
-      <c r="K64" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="L64" t="str"/>
+      <c r="K64" t="b">
+        <v>1</v>
+      </c>
       <c r="M64" t="n">
         <v>12</v>
       </c>
       <c r="N64" t="n">
         <v>3</v>
       </c>
-      <c r="O64" s="6" t="b">
+      <c r="O64" t="b">
         <v>1</v>
       </c>
       <c r="P64" t="inlineStr">
@@ -5546,21 +5687,26 @@
           <t>Cafe</t>
         </is>
       </c>
-      <c r="Q64" t="str">
-        <v>3,9,10,11</v>
-      </c>
-      <c r="R64" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="S64" t="str">
-        <v>1,2,3,4,5,6,7,8,9,10,11</v>
-      </c>
-      <c r="T64" t="str">
-        <v>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16</v>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>3,9,10,11</t>
+        </is>
+      </c>
+      <c r="R64" t="b">
+        <v>1</v>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16</t>
+        </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="str"/>
       <c r="B65" t="n">
         <v>2501</v>
       </c>
@@ -5570,8 +5716,10 @@
       <c r="D65" t="n">
         <v>600</v>
       </c>
-      <c r="E65" t="str">
-        <v>10,20,30</v>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>10,20,30</t>
+        </is>
       </c>
       <c r="F65" t="n">
         <v>1</v>
@@ -5579,8 +5727,10 @@
       <c r="G65" t="n">
         <v>10</v>
       </c>
-      <c r="H65" t="str">
-        <v>4,5,6</v>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>4,5,6</t>
+        </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -5590,7 +5740,7 @@
       <c r="J65" t="n">
         <v>2</v>
       </c>
-      <c r="K65" s="6" t="b">
+      <c r="K65" t="b">
         <v>1</v>
       </c>
       <c r="L65" t="inlineStr">
@@ -5604,7 +5754,7 @@
       <c r="N65" t="n">
         <v>1</v>
       </c>
-      <c r="O65" s="6" t="b">
+      <c r="O65" t="b">
         <v>0</v>
       </c>
       <c r="P65" t="inlineStr">
@@ -5612,21 +5762,26 @@
           <t>Cafe</t>
         </is>
       </c>
-      <c r="Q65" t="str">
-        <v>3,9</v>
-      </c>
-      <c r="R65" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="S65" t="str">
-        <v>1,2,3,4,5,6,7,8,9,10,11</v>
-      </c>
-      <c r="T65" t="str">
-        <v>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16</v>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>3,9</t>
+        </is>
+      </c>
+      <c r="R65" t="b">
+        <v>1</v>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16</t>
+        </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="str"/>
       <c r="B66" t="n">
         <v>2502</v>
       </c>
@@ -5636,8 +5791,10 @@
       <c r="D66" t="n">
         <v>750</v>
       </c>
-      <c r="E66" t="str">
-        <v>10,20,30</v>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>10,20,30</t>
+        </is>
       </c>
       <c r="F66" t="n">
         <v>1</v>
@@ -5645,8 +5802,10 @@
       <c r="G66" t="n">
         <v>10</v>
       </c>
-      <c r="H66" t="str">
-        <v>1,4,5,6,7,8</v>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>1,4,5,6,7,8</t>
+        </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -5656,7 +5815,7 @@
       <c r="J66" t="n">
         <v>2</v>
       </c>
-      <c r="K66" s="6" t="b">
+      <c r="K66" t="b">
         <v>1</v>
       </c>
       <c r="L66" t="inlineStr">
@@ -5670,7 +5829,7 @@
       <c r="N66" t="n">
         <v>2</v>
       </c>
-      <c r="O66" s="6" t="b">
+      <c r="O66" t="b">
         <v>0</v>
       </c>
       <c r="P66" t="inlineStr">
@@ -5678,21 +5837,26 @@
           <t>Cafe</t>
         </is>
       </c>
-      <c r="Q66" t="str">
-        <v>3,9,10</v>
-      </c>
-      <c r="R66" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="S66" t="str">
-        <v>1,2,3,4,5,6,7,8,9,10,11</v>
-      </c>
-      <c r="T66" t="str">
-        <v>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16</v>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>3,9,10</t>
+        </is>
+      </c>
+      <c r="R66" t="b">
+        <v>1</v>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16</t>
+        </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="str"/>
       <c r="B67" t="n">
         <v>2503</v>
       </c>
@@ -5702,8 +5866,10 @@
       <c r="D67" t="n">
         <v>900</v>
       </c>
-      <c r="E67" t="str">
-        <v>10,20,30</v>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>10,20,30</t>
+        </is>
       </c>
       <c r="F67" t="n">
         <v>1</v>
@@ -5711,8 +5877,10 @@
       <c r="G67" t="n">
         <v>10</v>
       </c>
-      <c r="H67" t="str">
-        <v>1,2,4,5,6,7,8</v>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>1,2,4,5,6,7,8</t>
+        </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -5722,17 +5890,16 @@
       <c r="J67" t="n">
         <v>2</v>
       </c>
-      <c r="K67" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="L67" t="str"/>
+      <c r="K67" t="b">
+        <v>1</v>
+      </c>
       <c r="M67" t="n">
         <v>22</v>
       </c>
       <c r="N67" t="n">
         <v>3</v>
       </c>
-      <c r="O67" s="6" t="b">
+      <c r="O67" t="b">
         <v>1</v>
       </c>
       <c r="P67" t="inlineStr">
@@ -5740,17 +5907,1283 @@
           <t>Cafe</t>
         </is>
       </c>
-      <c r="Q67" t="str">
-        <v>3,9,10,11</v>
-      </c>
-      <c r="R67" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="S67" t="str">
-        <v>1,2,3,4,5,6,7,8,9,10,11</v>
-      </c>
-      <c r="T67" t="str">
-        <v>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16</v>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>3,9,10,11</t>
+        </is>
+      </c>
+      <c r="R67" t="b">
+        <v>1</v>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" t="n">
+        <v>1601</v>
+      </c>
+      <c r="C68" t="n">
+        <v>1602</v>
+      </c>
+      <c r="D68" t="n">
+        <v>600</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>10,20,30</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>1</v>
+      </c>
+      <c r="G68" t="n">
+        <v>10</v>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>19,20</t>
+        </is>
+      </c>
+      <c r="J68" t="n">
+        <v>2</v>
+      </c>
+      <c r="K68" t="b">
+        <v>1</v>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M68" t="n">
+        <v>1</v>
+      </c>
+      <c r="N68" t="n">
+        <v>1</v>
+      </c>
+      <c r="O68" t="b">
+        <v>0</v>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Steamed</t>
+        </is>
+      </c>
+      <c r="R68" t="b">
+        <v>1</v>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,17</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" t="n">
+        <v>1602</v>
+      </c>
+      <c r="C69" t="n">
+        <v>1603</v>
+      </c>
+      <c r="D69" t="n">
+        <v>600</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>10,20,30</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>1</v>
+      </c>
+      <c r="G69" t="n">
+        <v>10</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>19,20</t>
+        </is>
+      </c>
+      <c r="J69" t="n">
+        <v>2</v>
+      </c>
+      <c r="K69" t="b">
+        <v>1</v>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M69" t="n">
+        <v>1</v>
+      </c>
+      <c r="N69" t="n">
+        <v>2</v>
+      </c>
+      <c r="O69" t="b">
+        <v>0</v>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Steamed</t>
+        </is>
+      </c>
+      <c r="R69" t="b">
+        <v>1</v>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,17</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" t="n">
+        <v>1603</v>
+      </c>
+      <c r="C70" t="n">
+        <v>0</v>
+      </c>
+      <c r="D70" t="n">
+        <v>600</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>10,20,30</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>1</v>
+      </c>
+      <c r="G70" t="n">
+        <v>10</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>19,20</t>
+        </is>
+      </c>
+      <c r="J70" t="n">
+        <v>2</v>
+      </c>
+      <c r="K70" t="b">
+        <v>1</v>
+      </c>
+      <c r="M70" t="n">
+        <v>1</v>
+      </c>
+      <c r="N70" t="n">
+        <v>3</v>
+      </c>
+      <c r="O70" t="b">
+        <v>1</v>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Steamed</t>
+        </is>
+      </c>
+      <c r="R70" t="b">
+        <v>1</v>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,17</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" t="n">
+        <v>2601</v>
+      </c>
+      <c r="C71" t="n">
+        <v>2602</v>
+      </c>
+      <c r="D71" t="n">
+        <v>600</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>10,20,30</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>1</v>
+      </c>
+      <c r="G71" t="n">
+        <v>10</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>19,20</t>
+        </is>
+      </c>
+      <c r="J71" t="n">
+        <v>2</v>
+      </c>
+      <c r="K71" t="b">
+        <v>1</v>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M71" t="n">
+        <v>2</v>
+      </c>
+      <c r="N71" t="n">
+        <v>1</v>
+      </c>
+      <c r="O71" t="b">
+        <v>0</v>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Steamed</t>
+        </is>
+      </c>
+      <c r="R71" t="b">
+        <v>1</v>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,17</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" t="n">
+        <v>2602</v>
+      </c>
+      <c r="C72" t="n">
+        <v>2603</v>
+      </c>
+      <c r="D72" t="n">
+        <v>600</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>10,20,30</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>1</v>
+      </c>
+      <c r="G72" t="n">
+        <v>10</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>19,20</t>
+        </is>
+      </c>
+      <c r="J72" t="n">
+        <v>2</v>
+      </c>
+      <c r="K72" t="b">
+        <v>1</v>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M72" t="n">
+        <v>2</v>
+      </c>
+      <c r="N72" t="n">
+        <v>2</v>
+      </c>
+      <c r="O72" t="b">
+        <v>0</v>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Steamed</t>
+        </is>
+      </c>
+      <c r="R72" t="b">
+        <v>1</v>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,17</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" t="n">
+        <v>2603</v>
+      </c>
+      <c r="C73" t="n">
+        <v>0</v>
+      </c>
+      <c r="D73" t="n">
+        <v>600</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>10,20,30</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>1</v>
+      </c>
+      <c r="G73" t="n">
+        <v>10</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>19,20</t>
+        </is>
+      </c>
+      <c r="J73" t="n">
+        <v>2</v>
+      </c>
+      <c r="K73" t="b">
+        <v>1</v>
+      </c>
+      <c r="M73" t="n">
+        <v>2</v>
+      </c>
+      <c r="N73" t="n">
+        <v>3</v>
+      </c>
+      <c r="O73" t="b">
+        <v>1</v>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Steamed</t>
+        </is>
+      </c>
+      <c r="R73" t="b">
+        <v>1</v>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,17</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" t="n">
+        <v>1701</v>
+      </c>
+      <c r="C74" t="n">
+        <v>1702</v>
+      </c>
+      <c r="D74" t="n">
+        <v>900</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>10,20,30</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>1</v>
+      </c>
+      <c r="G74" t="n">
+        <v>10</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>13,14,15</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>21,22</t>
+        </is>
+      </c>
+      <c r="J74" t="n">
+        <v>2</v>
+      </c>
+      <c r="K74" t="b">
+        <v>1</v>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M74" t="n">
+        <v>1</v>
+      </c>
+      <c r="N74" t="n">
+        <v>1</v>
+      </c>
+      <c r="O74" t="b">
+        <v>0</v>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Tea</t>
+        </is>
+      </c>
+      <c r="R74" t="b">
+        <v>1</v>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>13,14,15</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11,18,19,20,21</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" t="n">
+        <v>1702</v>
+      </c>
+      <c r="C75" t="n">
+        <v>1703</v>
+      </c>
+      <c r="D75" t="n">
+        <v>900</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>10,20,30</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>1</v>
+      </c>
+      <c r="G75" t="n">
+        <v>10</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>13,14,15</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>21,22</t>
+        </is>
+      </c>
+      <c r="J75" t="n">
+        <v>2</v>
+      </c>
+      <c r="K75" t="b">
+        <v>1</v>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M75" t="n">
+        <v>1</v>
+      </c>
+      <c r="N75" t="n">
+        <v>2</v>
+      </c>
+      <c r="O75" t="b">
+        <v>0</v>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Tea</t>
+        </is>
+      </c>
+      <c r="R75" t="b">
+        <v>1</v>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>13,14,15</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11,18,19,20,21</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" t="n">
+        <v>1703</v>
+      </c>
+      <c r="C76" t="n">
+        <v>0</v>
+      </c>
+      <c r="D76" t="n">
+        <v>900</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>10,20,30</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>1</v>
+      </c>
+      <c r="G76" t="n">
+        <v>10</v>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>13,14,15</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>21,22</t>
+        </is>
+      </c>
+      <c r="J76" t="n">
+        <v>2</v>
+      </c>
+      <c r="K76" t="b">
+        <v>1</v>
+      </c>
+      <c r="M76" t="n">
+        <v>1</v>
+      </c>
+      <c r="N76" t="n">
+        <v>3</v>
+      </c>
+      <c r="O76" t="b">
+        <v>1</v>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Tea</t>
+        </is>
+      </c>
+      <c r="R76" t="b">
+        <v>1</v>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>13,14,15</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11,18,19,20,21</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" t="n">
+        <v>2701</v>
+      </c>
+      <c r="C77" t="n">
+        <v>2702</v>
+      </c>
+      <c r="D77" t="n">
+        <v>900</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>10,20,30</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>1</v>
+      </c>
+      <c r="G77" t="n">
+        <v>10</v>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>13,14,15</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>21,22</t>
+        </is>
+      </c>
+      <c r="J77" t="n">
+        <v>2</v>
+      </c>
+      <c r="K77" t="b">
+        <v>1</v>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M77" t="n">
+        <v>2</v>
+      </c>
+      <c r="N77" t="n">
+        <v>1</v>
+      </c>
+      <c r="O77" t="b">
+        <v>0</v>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Tea</t>
+        </is>
+      </c>
+      <c r="R77" t="b">
+        <v>1</v>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>13,14,15</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11,18,19,20,21</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" t="n">
+        <v>2702</v>
+      </c>
+      <c r="C78" t="n">
+        <v>2703</v>
+      </c>
+      <c r="D78" t="n">
+        <v>900</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>10,20,30</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
+        <v>1</v>
+      </c>
+      <c r="G78" t="n">
+        <v>10</v>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>13,14,15</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>21,22</t>
+        </is>
+      </c>
+      <c r="J78" t="n">
+        <v>2</v>
+      </c>
+      <c r="K78" t="b">
+        <v>1</v>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M78" t="n">
+        <v>2</v>
+      </c>
+      <c r="N78" t="n">
+        <v>2</v>
+      </c>
+      <c r="O78" t="b">
+        <v>0</v>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Tea</t>
+        </is>
+      </c>
+      <c r="R78" t="b">
+        <v>1</v>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>13,14,15</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11,18,19,20,21</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" t="n">
+        <v>2703</v>
+      </c>
+      <c r="C79" t="n">
+        <v>0</v>
+      </c>
+      <c r="D79" t="n">
+        <v>900</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>10,20,30</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>1</v>
+      </c>
+      <c r="G79" t="n">
+        <v>10</v>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>13,14,15</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>21,22</t>
+        </is>
+      </c>
+      <c r="J79" t="n">
+        <v>2</v>
+      </c>
+      <c r="K79" t="b">
+        <v>1</v>
+      </c>
+      <c r="M79" t="n">
+        <v>2</v>
+      </c>
+      <c r="N79" t="n">
+        <v>3</v>
+      </c>
+      <c r="O79" t="b">
+        <v>1</v>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Tea</t>
+        </is>
+      </c>
+      <c r="R79" t="b">
+        <v>1</v>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>13,14,15</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11,18,19,20,21</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" t="n">
+        <v>1801</v>
+      </c>
+      <c r="C80" t="n">
+        <v>1802</v>
+      </c>
+      <c r="D80" t="n">
+        <v>600</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>10,20,30</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>1</v>
+      </c>
+      <c r="G80" t="n">
+        <v>10</v>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>19,20,21,22</t>
+        </is>
+      </c>
+      <c r="J80" t="n">
+        <v>2</v>
+      </c>
+      <c r="K80" t="b">
+        <v>1</v>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M80" t="n">
+        <v>13</v>
+      </c>
+      <c r="N80" t="n">
+        <v>1</v>
+      </c>
+      <c r="O80" t="b">
+        <v>0</v>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>SteamTea</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="R80" t="b">
+        <v>1</v>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>12,13,14,15</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11,17,18,19,20,21</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" t="n">
+        <v>1802</v>
+      </c>
+      <c r="C81" t="n">
+        <v>1803</v>
+      </c>
+      <c r="D81" t="n">
+        <v>750</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>10,20,30</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>1</v>
+      </c>
+      <c r="G81" t="n">
+        <v>10</v>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>19,20,21,22</t>
+        </is>
+      </c>
+      <c r="J81" t="n">
+        <v>2</v>
+      </c>
+      <c r="K81" t="b">
+        <v>1</v>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M81" t="n">
+        <v>13</v>
+      </c>
+      <c r="N81" t="n">
+        <v>2</v>
+      </c>
+      <c r="O81" t="b">
+        <v>0</v>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>SteamTea</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>13,14</t>
+        </is>
+      </c>
+      <c r="R81" t="b">
+        <v>1</v>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>12,13,14,15</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11,17,18,19,20,21</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" t="n">
+        <v>1803</v>
+      </c>
+      <c r="C82" t="n">
+        <v>0</v>
+      </c>
+      <c r="D82" t="n">
+        <v>900</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>10,20,30</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v>1</v>
+      </c>
+      <c r="G82" t="n">
+        <v>10</v>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>19,20,21,22</t>
+        </is>
+      </c>
+      <c r="J82" t="n">
+        <v>2</v>
+      </c>
+      <c r="K82" t="b">
+        <v>1</v>
+      </c>
+      <c r="M82" t="n">
+        <v>13</v>
+      </c>
+      <c r="N82" t="n">
+        <v>3</v>
+      </c>
+      <c r="O82" t="b">
+        <v>1</v>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>SteamTea</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>13,14,15</t>
+        </is>
+      </c>
+      <c r="R82" t="b">
+        <v>1</v>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>12,13,14,15</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11,17,18,19,20,21</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" t="n">
+        <v>2801</v>
+      </c>
+      <c r="C83" t="n">
+        <v>2802</v>
+      </c>
+      <c r="D83" t="n">
+        <v>600</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>10,20,30</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>1</v>
+      </c>
+      <c r="G83" t="n">
+        <v>10</v>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>19,20,21,22</t>
+        </is>
+      </c>
+      <c r="J83" t="n">
+        <v>2</v>
+      </c>
+      <c r="K83" t="b">
+        <v>1</v>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M83" t="n">
+        <v>23</v>
+      </c>
+      <c r="N83" t="n">
+        <v>1</v>
+      </c>
+      <c r="O83" t="b">
+        <v>0</v>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>SteamTea</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="R83" t="b">
+        <v>1</v>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>12,13,14,15</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11,17,18,19,20,21</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" t="n">
+        <v>2802</v>
+      </c>
+      <c r="C84" t="n">
+        <v>2803</v>
+      </c>
+      <c r="D84" t="n">
+        <v>750</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>10,20,30</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>1</v>
+      </c>
+      <c r="G84" t="n">
+        <v>10</v>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>19,20,21,22</t>
+        </is>
+      </c>
+      <c r="J84" t="n">
+        <v>2</v>
+      </c>
+      <c r="K84" t="b">
+        <v>1</v>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M84" t="n">
+        <v>23</v>
+      </c>
+      <c r="N84" t="n">
+        <v>2</v>
+      </c>
+      <c r="O84" t="b">
+        <v>0</v>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>SteamTea</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>13,14</t>
+        </is>
+      </c>
+      <c r="R84" t="b">
+        <v>1</v>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>12,13,14,15</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11,17,18,19,20,21</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" t="n">
+        <v>2803</v>
+      </c>
+      <c r="C85" t="n">
+        <v>0</v>
+      </c>
+      <c r="D85" t="n">
+        <v>900</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>10,20,30</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>1</v>
+      </c>
+      <c r="G85" t="n">
+        <v>10</v>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>19,20,21,22</t>
+        </is>
+      </c>
+      <c r="J85" t="n">
+        <v>2</v>
+      </c>
+      <c r="K85" t="b">
+        <v>1</v>
+      </c>
+      <c r="M85" t="n">
+        <v>23</v>
+      </c>
+      <c r="N85" t="n">
+        <v>3</v>
+      </c>
+      <c r="O85" t="b">
+        <v>1</v>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>SteamTea</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>13,14,15</t>
+        </is>
+      </c>
+      <c r="R85" t="b">
+        <v>1</v>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>12,13,14,15</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11,17,18,19,20,21</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/Design/Excel/ET/Datas/Product/LevelConfig.xlsx
+++ b/Design/Excel/ET/Datas/Product/LevelConfig.xlsx
@@ -3414,7 +3414,7 @@
         <v>1102</v>
       </c>
       <c r="D32" t="n">
-        <v>500</v>
+        <v>1800</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -3484,7 +3484,7 @@
         <v>1103</v>
       </c>
       <c r="D33" t="n">
-        <v>650</v>
+        <v>2100</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -3554,7 +3554,7 @@
         <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>800</v>
+        <v>2400</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
